--- a/research/traditional_assets/database/data/nigeria/nigeria_information_services.xlsx
+++ b/research/traditional_assets/database/data/nigeria/nigeria_information_services.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="ngse_etranzact" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,46 +590,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.1016</v>
+        <v>0.1195</v>
       </c>
       <c r="E2">
-        <v>-0.0002</v>
+        <v>0.00615</v>
       </c>
       <c r="G2">
-        <v>-0.0511643719190889</v>
+        <v>0.02229668538308277</v>
       </c>
       <c r="H2">
-        <v>-0.0511643719190889</v>
+        <v>0.02229668538308277</v>
       </c>
       <c r="I2">
-        <v>-0.03358830528641849</v>
+        <v>0.04968302843687739</v>
       </c>
       <c r="J2">
-        <v>-0.02814684324118286</v>
+        <v>0.03536113982267967</v>
       </c>
       <c r="K2">
-        <v>-0.5600000000000001</v>
+        <v>6.199999999999999</v>
       </c>
       <c r="L2">
-        <v>-0.009518952915179332</v>
+        <v>0.1122984966491578</v>
       </c>
       <c r="M2">
-        <v>2.44</v>
+        <v>2.31</v>
       </c>
       <c r="N2">
-        <v>0.03986928104575163</v>
+        <v>0.02340425531914894</v>
       </c>
       <c r="O2">
-        <v>-4.357142857142857</v>
+        <v>0.3725806451612904</v>
       </c>
       <c r="P2">
-        <v>2.44</v>
+        <v>2.31</v>
       </c>
       <c r="Q2">
-        <v>0.03986928104575163</v>
+        <v>0.02340425531914894</v>
       </c>
       <c r="R2">
-        <v>-4.357142857142857</v>
+        <v>0.3725806451612904</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +638,67 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>24.92</v>
+        <v>31.72</v>
       </c>
       <c r="V2">
-        <v>0.4071895424836601</v>
+        <v>0.3213779128672746</v>
       </c>
       <c r="W2">
-        <v>10.00965836526181</v>
+        <v>0.3411009407576914</v>
       </c>
       <c r="X2">
-        <v>0.1322337410083892</v>
+        <v>0.269941717145221</v>
       </c>
       <c r="Y2">
-        <v>9.877424624253424</v>
+        <v>0.07115922361247035</v>
       </c>
       <c r="Z2">
-        <v>5.58583364982909</v>
-      </c>
-      <c r="AA2">
-        <v>0.003595534591265683</v>
+        <v>3.782024934922592</v>
       </c>
       <c r="AB2">
-        <v>0.1310250923400502</v>
-      </c>
-      <c r="AC2">
-        <v>-0.1274295577487844</v>
+        <v>0.2689985063876479</v>
       </c>
       <c r="AD2">
-        <v>0.959</v>
+        <v>0.75</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.959</v>
+        <v>0.75</v>
       </c>
       <c r="AG2">
-        <v>-23.961</v>
+        <v>-30.97</v>
       </c>
       <c r="AH2">
-        <v>0.0154281761289596</v>
+        <v>0.007541478129713424</v>
       </c>
       <c r="AI2">
-        <v>0.03579827541154952</v>
+        <v>0.01775147928994083</v>
       </c>
       <c r="AJ2">
-        <v>-0.6434383307822444</v>
+        <v>-0.4572567547615532</v>
       </c>
       <c r="AK2">
-        <v>-12.82022471910115</v>
+        <v>-2.941120607787274</v>
       </c>
       <c r="AL2">
-        <v>0.052</v>
+        <v>0.079</v>
       </c>
       <c r="AM2">
-        <v>-5.774000000000001</v>
+        <v>-5.987</v>
       </c>
       <c r="AN2">
-        <v>-0.855486173059768</v>
+        <v>0.2068394925537783</v>
       </c>
       <c r="AO2">
-        <v>-37.99999999999999</v>
+        <v>34.72151898734177</v>
       </c>
       <c r="AP2">
-        <v>21.37466547725246</v>
+        <v>-8.541092112520683</v>
       </c>
       <c r="AQ2">
-        <v>0.3422237616903359</v>
+        <v>-0.4581593452480375</v>
       </c>
     </row>
     <row r="3">
@@ -722,25 +718,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.187</v>
+        <v>0.138</v>
       </c>
       <c r="G3">
-        <v>-0.03197158081705151</v>
+        <v>0.03196881091617933</v>
       </c>
       <c r="H3">
-        <v>-0.03197158081705151</v>
+        <v>0.03196881091617933</v>
       </c>
       <c r="I3">
-        <v>-0.009520426287744228</v>
+        <v>0.0571150097465887</v>
       </c>
       <c r="J3">
-        <v>-0.009520426287744228</v>
+        <v>0.04224569134513969</v>
       </c>
       <c r="K3">
-        <v>-3.46</v>
+        <v>2.61</v>
       </c>
       <c r="L3">
-        <v>-0.06145648312611013</v>
+        <v>0.05087719298245614</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -749,7 +745,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -758,79 +754,70 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>18.8</v>
+        <v>28.5</v>
       </c>
       <c r="V3">
-        <v>0.618421052631579</v>
+        <v>0.3963838664812239</v>
       </c>
       <c r="W3">
-        <v>19.88505747126437</v>
+        <v>0.5087719298245614</v>
       </c>
       <c r="X3">
-        <v>0.1334652015260077</v>
+        <v>0.270695690968867</v>
       </c>
       <c r="Y3">
-        <v>19.75159226973836</v>
-      </c>
-      <c r="Z3">
-        <v>-5.812512905224034</v>
-      </c>
-      <c r="AA3">
-        <v>0.05533760066074747</v>
+        <v>0.2380762388556944</v>
       </c>
       <c r="AB3">
-        <v>0.1310938418767729</v>
-      </c>
-      <c r="AC3">
-        <v>-0.07575624121602548</v>
+        <v>0.2689505247524282</v>
       </c>
       <c r="AD3">
-        <v>0.9409999999999999</v>
+        <v>0.729</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.9409999999999999</v>
+        <v>0.729</v>
       </c>
       <c r="AG3">
-        <v>-17.859</v>
+        <v>-27.771</v>
       </c>
       <c r="AH3">
-        <v>0.03002456845665422</v>
+        <v>0.01003731291908191</v>
       </c>
       <c r="AI3">
-        <v>0.1549991764124526</v>
+        <v>0.03417881757231937</v>
       </c>
       <c r="AJ3">
-        <v>-1.424049118890041</v>
+        <v>-0.6293140565161232</v>
       </c>
       <c r="AK3">
-        <v>1.403016733443318</v>
+        <v>3.87268163436062</v>
       </c>
       <c r="AL3">
-        <v>0.049</v>
+        <v>0.076</v>
       </c>
       <c r="AM3">
-        <v>-0.157</v>
+        <v>-0.48</v>
       </c>
       <c r="AN3">
-        <v>4.728643216080402</v>
+        <v>0.1964959568733154</v>
       </c>
       <c r="AO3">
-        <v>-10.93877551020408</v>
+        <v>38.55263157894737</v>
       </c>
       <c r="AP3">
-        <v>-89.74371859296483</v>
+        <v>-7.48544474393531</v>
       </c>
       <c r="AQ3">
-        <v>3.414012738853504</v>
+        <v>-6.104166666666667</v>
       </c>
     </row>
     <row r="4">
@@ -850,46 +837,46 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0162</v>
+        <v>0.101</v>
       </c>
       <c r="E4">
-        <v>-0.0002</v>
+        <v>0.00615</v>
       </c>
       <c r="G4">
-        <v>-0.4782608695652174</v>
+        <v>-0.1046035805626598</v>
       </c>
       <c r="H4">
-        <v>-0.4782608695652174</v>
+        <v>-0.1046035805626598</v>
       </c>
       <c r="I4">
-        <v>-0.5691699604743083</v>
+        <v>-0.04782608695652174</v>
       </c>
       <c r="J4">
-        <v>-0.384753586334614</v>
+        <v>-0.03270393374741201</v>
       </c>
       <c r="K4">
-        <v>2.9</v>
+        <v>3.59</v>
       </c>
       <c r="L4">
-        <v>1.146245059288538</v>
+        <v>0.918158567774936</v>
       </c>
       <c r="M4">
-        <v>2.44</v>
+        <v>2.31</v>
       </c>
       <c r="N4">
-        <v>0.07922077922077922</v>
+        <v>0.08619402985074627</v>
       </c>
       <c r="O4">
-        <v>0.8413793103448276</v>
+        <v>0.6434540389972145</v>
       </c>
       <c r="P4">
-        <v>2.44</v>
+        <v>2.31</v>
       </c>
       <c r="Q4">
-        <v>0.07922077922077922</v>
+        <v>0.08619402985074627</v>
       </c>
       <c r="R4">
-        <v>0.8413793103448276</v>
+        <v>0.6434540389972145</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -898,73 +885,8785 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>6.12</v>
+        <v>3.22</v>
       </c>
       <c r="V4">
-        <v>0.1987012987012987</v>
+        <v>0.1201492537313433</v>
       </c>
       <c r="W4">
-        <v>0.1342592592592592</v>
+        <v>0.1734299516908213</v>
       </c>
       <c r="X4">
-        <v>0.1310022804907708</v>
+        <v>0.269187743321575</v>
       </c>
       <c r="Y4">
-        <v>0.003256978768488489</v>
+        <v>-0.09575779163075376</v>
       </c>
       <c r="Z4">
-        <v>0.1251360174102285</v>
+        <v>0.2678449102616797</v>
       </c>
       <c r="AA4">
-        <v>-0.0481465314782161</v>
+        <v>-0.008759582199779488</v>
       </c>
       <c r="AB4">
-        <v>0.1309563428033274</v>
+        <v>0.2690464880228676</v>
       </c>
       <c r="AC4">
-        <v>-0.1791028742815435</v>
+        <v>-0.2778060702226471</v>
       </c>
       <c r="AD4">
-        <v>0.018</v>
+        <v>0.021</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.018</v>
+        <v>0.021</v>
       </c>
       <c r="AG4">
-        <v>-6.102</v>
+        <v>-3.199</v>
       </c>
       <c r="AH4">
-        <v>0.0005840742423259133</v>
+        <v>0.000782968569404571</v>
       </c>
       <c r="AI4">
-        <v>0.0008688097306689834</v>
+        <v>0.001003776110128579</v>
       </c>
       <c r="AJ4">
-        <v>-0.2470645396388371</v>
+        <v>-0.1355451040210161</v>
       </c>
       <c r="AK4">
-        <v>-0.4180024660912454</v>
+        <v>-0.1807242528670697</v>
       </c>
       <c r="AL4">
         <v>0.003</v>
       </c>
       <c r="AM4">
-        <v>-5.617</v>
+        <v>-5.507</v>
       </c>
       <c r="AN4">
-        <v>-0.01363636363636363</v>
+        <v>-0.25</v>
       </c>
       <c r="AO4">
-        <v>-480</v>
+        <v>-62.33333333333333</v>
       </c>
       <c r="AP4">
-        <v>4.622727272727273</v>
+        <v>38.08333333333334</v>
       </c>
       <c r="AQ4">
-        <v>0.2563646074416949</v>
+        <v>0.03395678227710187</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>eTranzact International Plc (NGSE:ETRANZACT)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>NGSE:ETRANZACT</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Information Services</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.0100373129190819</v>
+      </c>
+      <c r="F2">
+        <v>0.18</v>
+      </c>
+      <c r="G2">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="H2">
+        <v>61.848989456521</v>
+      </c>
+      <c r="I2">
+        <v>44.129</v>
+      </c>
+      <c r="J2">
+        <v>46.422209456521</v>
+      </c>
+      <c r="K2">
+        <v>0.729</v>
+      </c>
+      <c r="L2">
+        <v>13.07322</v>
+      </c>
+      <c r="M2">
+        <v>0.268950524752428</v>
+      </c>
+      <c r="N2">
+        <v>0.257581325268723</v>
+      </c>
+      <c r="O2">
+        <v>0.09682782110091739</v>
+      </c>
+      <c r="P2">
+        <v>0.0441</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.270695690968867</v>
+      </c>
+      <c r="T2">
+        <v>0.304443079596004</v>
+      </c>
+      <c r="U2">
+        <v>1.35355865606369</v>
+      </c>
+      <c r="V2">
+        <v>1.55053976340966</v>
+      </c>
+      <c r="W2">
+        <v>3.55749666172041</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="AB2">
+        <v>0.1713229714353474</v>
+      </c>
+      <c r="AC2">
+        <v>0.1383254587155963</v>
+      </c>
+      <c r="AD2">
+        <v>0.3</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>3.71</v>
+      </c>
+      <c r="AH2">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="AI2">
+        <v>1.629</v>
+      </c>
+      <c r="AJ2">
+        <v>0.729</v>
+      </c>
+      <c r="AK2">
+        <v>0.729</v>
+      </c>
+      <c r="AL2">
+        <v>0.076</v>
+      </c>
+      <c r="AM2">
+        <v>0.7289999999999999</v>
+      </c>
+      <c r="AN2">
+        <v>28.5</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.26906144320161</v>
+      </c>
+      <c r="C2">
+        <v>72.6077427709308</v>
+      </c>
+      <c r="D2">
+        <v>44.1077427709308</v>
+      </c>
+      <c r="E2">
+        <v>-0.729</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>28.5</v>
+      </c>
+      <c r="H2">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>3.71</v>
+      </c>
+      <c r="K2">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L2">
+        <v>2.93</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>2.93</v>
+      </c>
+      <c r="O2">
+        <v>0.8790000000000002</v>
+      </c>
+      <c r="P2">
+        <v>2.051</v>
+      </c>
+      <c r="Q2">
+        <v>2.831</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.26906144320161</v>
+      </c>
+      <c r="T2">
+        <v>1.344019668071799</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.3</v>
+      </c>
+      <c r="W2">
+        <v>0.03199</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.2683025588720051</v>
+      </c>
+      <c r="C3">
+        <v>72.02730157962216</v>
+      </c>
+      <c r="D3">
+        <v>44.25359157962217</v>
+      </c>
+      <c r="E3">
+        <v>-0.002709999999999879</v>
+      </c>
+      <c r="F3">
+        <v>0.7262900000000001</v>
+      </c>
+      <c r="G3">
+        <v>28.5</v>
+      </c>
+      <c r="H3">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>3.71</v>
+      </c>
+      <c r="K3">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L3">
+        <v>2.93</v>
+      </c>
+      <c r="M3">
+        <v>0.03319145300000001</v>
+      </c>
+      <c r="N3">
+        <v>2.896808547</v>
+      </c>
+      <c r="O3">
+        <v>0.8690425641000001</v>
+      </c>
+      <c r="P3">
+        <v>2.0277659829</v>
+      </c>
+      <c r="Q3">
+        <v>2.8077659829</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.2706895544161668</v>
+      </c>
+      <c r="T3">
+        <v>1.353522837442003</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0.3</v>
+      </c>
+      <c r="W3">
+        <v>0.03199</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>88.27573773284342</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.2675436745424003</v>
+      </c>
+      <c r="C4">
+        <v>71.44782812983144</v>
+      </c>
+      <c r="D4">
+        <v>44.40040812983143</v>
+      </c>
+      <c r="E4">
+        <v>0.7235800000000002</v>
+      </c>
+      <c r="F4">
+        <v>1.45258</v>
+      </c>
+      <c r="G4">
+        <v>28.5</v>
+      </c>
+      <c r="H4">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>3.71</v>
+      </c>
+      <c r="K4">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L4">
+        <v>2.93</v>
+      </c>
+      <c r="M4">
+        <v>0.06638290600000002</v>
+      </c>
+      <c r="N4">
+        <v>2.863617094</v>
+      </c>
+      <c r="O4">
+        <v>0.8590851282000003</v>
+      </c>
+      <c r="P4">
+        <v>2.0045319658</v>
+      </c>
+      <c r="Q4">
+        <v>2.7845319658</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.2723508923902044</v>
+      </c>
+      <c r="T4">
+        <v>1.363219949044253</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0.3</v>
+      </c>
+      <c r="W4">
+        <v>0.03199</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>44.13786886642172</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.2667847902127954</v>
+      </c>
+      <c r="C5">
+        <v>70.86933208541214</v>
+      </c>
+      <c r="D5">
+        <v>44.54820208541214</v>
+      </c>
+      <c r="E5">
+        <v>1.44987</v>
+      </c>
+      <c r="F5">
+        <v>2.17887</v>
+      </c>
+      <c r="G5">
+        <v>28.5</v>
+      </c>
+      <c r="H5">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>3.71</v>
+      </c>
+      <c r="K5">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L5">
+        <v>2.93</v>
+      </c>
+      <c r="M5">
+        <v>0.099574359</v>
+      </c>
+      <c r="N5">
+        <v>2.830425641</v>
+      </c>
+      <c r="O5">
+        <v>0.8491276923000002</v>
+      </c>
+      <c r="P5">
+        <v>1.9812979487</v>
+      </c>
+      <c r="Q5">
+        <v>2.7612979487</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.2740464847554592</v>
+      </c>
+      <c r="T5">
+        <v>1.37311700109191</v>
+      </c>
+      <c r="U5">
+        <v>0.0457</v>
+      </c>
+      <c r="V5">
+        <v>0.3</v>
+      </c>
+      <c r="W5">
+        <v>0.03199</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>29.42524591094782</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.2660259058831906</v>
+      </c>
+      <c r="C6">
+        <v>70.29182323931839</v>
+      </c>
+      <c r="D6">
+        <v>44.69698323931839</v>
+      </c>
+      <c r="E6">
+        <v>2.17616</v>
+      </c>
+      <c r="F6">
+        <v>2.90516</v>
+      </c>
+      <c r="G6">
+        <v>28.5</v>
+      </c>
+      <c r="H6">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>3.71</v>
+      </c>
+      <c r="K6">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L6">
+        <v>2.93</v>
+      </c>
+      <c r="M6">
+        <v>0.132765812</v>
+      </c>
+      <c r="N6">
+        <v>2.797234188</v>
+      </c>
+      <c r="O6">
+        <v>0.8391702564000001</v>
+      </c>
+      <c r="P6">
+        <v>1.9580639316</v>
+      </c>
+      <c r="Q6">
+        <v>2.7380639316</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.2757774019616569</v>
+      </c>
+      <c r="T6">
+        <v>1.383220241723893</v>
+      </c>
+      <c r="U6">
+        <v>0.0457</v>
+      </c>
+      <c r="V6">
+        <v>0.3</v>
+      </c>
+      <c r="W6">
+        <v>0.03199</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>22.06893443321086</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.2652670215535857</v>
+      </c>
+      <c r="C7">
+        <v>69.71531151576779</v>
+      </c>
+      <c r="D7">
+        <v>44.8467615157678</v>
+      </c>
+      <c r="E7">
+        <v>2.90245</v>
+      </c>
+      <c r="F7">
+        <v>3.631450000000001</v>
+      </c>
+      <c r="G7">
+        <v>28.5</v>
+      </c>
+      <c r="H7">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>3.71</v>
+      </c>
+      <c r="K7">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L7">
+        <v>2.93</v>
+      </c>
+      <c r="M7">
+        <v>0.165957265</v>
+      </c>
+      <c r="N7">
+        <v>2.764042735</v>
+      </c>
+      <c r="O7">
+        <v>0.8292128205000002</v>
+      </c>
+      <c r="P7">
+        <v>1.9348299145</v>
+      </c>
+      <c r="Q7">
+        <v>2.7148299145</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.2775447595300903</v>
+      </c>
+      <c r="T7">
+        <v>1.393536182158654</v>
+      </c>
+      <c r="U7">
+        <v>0.0457</v>
+      </c>
+      <c r="V7">
+        <v>0.3</v>
+      </c>
+      <c r="W7">
+        <v>0.03199</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>17.65514754656869</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.2645081372239809</v>
+      </c>
+      <c r="C8">
+        <v>69.13980697244838</v>
+      </c>
+      <c r="D8">
+        <v>44.99754697244838</v>
+      </c>
+      <c r="E8">
+        <v>3.62874</v>
+      </c>
+      <c r="F8">
+        <v>4.35774</v>
+      </c>
+      <c r="G8">
+        <v>28.5</v>
+      </c>
+      <c r="H8">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>3.71</v>
+      </c>
+      <c r="K8">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L8">
+        <v>2.93</v>
+      </c>
+      <c r="M8">
+        <v>0.199148718</v>
+      </c>
+      <c r="N8">
+        <v>2.730851282</v>
+      </c>
+      <c r="O8">
+        <v>0.8192553846000001</v>
+      </c>
+      <c r="P8">
+        <v>1.9115958974</v>
+      </c>
+      <c r="Q8">
+        <v>2.6915958974</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.2793497204510436</v>
+      </c>
+      <c r="T8">
+        <v>1.404071610687773</v>
+      </c>
+      <c r="U8">
+        <v>0.0457</v>
+      </c>
+      <c r="V8">
+        <v>0.3</v>
+      </c>
+      <c r="W8">
+        <v>0.03199</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>14.71262295547391</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.2638276528943761</v>
+      </c>
+      <c r="C9">
+        <v>68.54958969591841</v>
+      </c>
+      <c r="D9">
+        <v>45.13361969591841</v>
+      </c>
+      <c r="E9">
+        <v>4.355030000000001</v>
+      </c>
+      <c r="F9">
+        <v>5.084030000000001</v>
+      </c>
+      <c r="G9">
+        <v>28.5</v>
+      </c>
+      <c r="H9">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>3.71</v>
+      </c>
+      <c r="K9">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L9">
+        <v>2.93</v>
+      </c>
+      <c r="M9">
+        <v>0.2404746190000001</v>
+      </c>
+      <c r="N9">
+        <v>2.689525381</v>
+      </c>
+      <c r="O9">
+        <v>0.8068576143000001</v>
+      </c>
+      <c r="P9">
+        <v>1.8826677667</v>
+      </c>
+      <c r="Q9">
+        <v>2.6626677667</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.2811934977358883</v>
+      </c>
+      <c r="T9">
+        <v>1.414833607572356</v>
+      </c>
+      <c r="U9">
+        <v>0.0473</v>
+      </c>
+      <c r="V9">
+        <v>0.3</v>
+      </c>
+      <c r="W9">
+        <v>0.03311</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>12.18423803802762</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.2630799685647713</v>
+      </c>
+      <c r="C10">
+        <v>67.97376208630007</v>
+      </c>
+      <c r="D10">
+        <v>45.28408208630007</v>
+      </c>
+      <c r="E10">
+        <v>5.081320000000001</v>
+      </c>
+      <c r="F10">
+        <v>5.810320000000001</v>
+      </c>
+      <c r="G10">
+        <v>28.5</v>
+      </c>
+      <c r="H10">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>3.71</v>
+      </c>
+      <c r="K10">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L10">
+        <v>2.93</v>
+      </c>
+      <c r="M10">
+        <v>0.2748281360000001</v>
+      </c>
+      <c r="N10">
+        <v>2.655171864</v>
+      </c>
+      <c r="O10">
+        <v>0.7965515592000002</v>
+      </c>
+      <c r="P10">
+        <v>1.8586203048</v>
+      </c>
+      <c r="Q10">
+        <v>2.6386203048</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.283077357135621</v>
+      </c>
+      <c r="T10">
+        <v>1.425829560910952</v>
+      </c>
+      <c r="U10">
+        <v>0.0473</v>
+      </c>
+      <c r="V10">
+        <v>0.3</v>
+      </c>
+      <c r="W10">
+        <v>0.03311</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>10.66120828327417</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.2625716842351665</v>
+      </c>
+      <c r="C11">
+        <v>67.35033223763547</v>
+      </c>
+      <c r="D11">
+        <v>45.38694223763547</v>
+      </c>
+      <c r="E11">
+        <v>5.80761</v>
+      </c>
+      <c r="F11">
+        <v>6.53661</v>
+      </c>
+      <c r="G11">
+        <v>28.5</v>
+      </c>
+      <c r="H11">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>3.71</v>
+      </c>
+      <c r="K11">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L11">
+        <v>2.93</v>
+      </c>
+      <c r="M11">
+        <v>0.334020771</v>
+      </c>
+      <c r="N11">
+        <v>2.595979229</v>
+      </c>
+      <c r="O11">
+        <v>0.7787937687000002</v>
+      </c>
+      <c r="P11">
+        <v>1.8171854603</v>
+      </c>
+      <c r="Q11">
+        <v>2.5971854603</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.2850026200386445</v>
+      </c>
+      <c r="T11">
+        <v>1.437067183553693</v>
+      </c>
+      <c r="U11">
+        <v>0.0511</v>
+      </c>
+      <c r="V11">
+        <v>0.3</v>
+      </c>
+      <c r="W11">
+        <v>0.03577</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>8.771909576844848</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.2618505999055616</v>
+      </c>
+      <c r="C12">
+        <v>66.77077043666338</v>
+      </c>
+      <c r="D12">
+        <v>45.53367043666339</v>
+      </c>
+      <c r="E12">
+        <v>6.533900000000001</v>
+      </c>
+      <c r="F12">
+        <v>7.262900000000001</v>
+      </c>
+      <c r="G12">
+        <v>28.5</v>
+      </c>
+      <c r="H12">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>3.71</v>
+      </c>
+      <c r="K12">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L12">
+        <v>2.93</v>
+      </c>
+      <c r="M12">
+        <v>0.37113419</v>
+      </c>
+      <c r="N12">
+        <v>2.55886581</v>
+      </c>
+      <c r="O12">
+        <v>0.7676597430000002</v>
+      </c>
+      <c r="P12">
+        <v>1.791206067</v>
+      </c>
+      <c r="Q12">
+        <v>2.571206067</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.2869706665617351</v>
+      </c>
+      <c r="T12">
+        <v>1.44855453114405</v>
+      </c>
+      <c r="U12">
+        <v>0.0511</v>
+      </c>
+      <c r="V12">
+        <v>0.3</v>
+      </c>
+      <c r="W12">
+        <v>0.03577</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>7.894718619160364</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.2612758155759568</v>
+      </c>
+      <c r="C13">
+        <v>66.16212037055294</v>
+      </c>
+      <c r="D13">
+        <v>45.65131037055296</v>
+      </c>
+      <c r="E13">
+        <v>7.260190000000001</v>
+      </c>
+      <c r="F13">
+        <v>7.989190000000001</v>
+      </c>
+      <c r="G13">
+        <v>28.5</v>
+      </c>
+      <c r="H13">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>3.71</v>
+      </c>
+      <c r="K13">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L13">
+        <v>2.93</v>
+      </c>
+      <c r="M13">
+        <v>0.4234270700000001</v>
+      </c>
+      <c r="N13">
+        <v>2.50657293</v>
+      </c>
+      <c r="O13">
+        <v>0.7519718790000001</v>
+      </c>
+      <c r="P13">
+        <v>1.754601051</v>
+      </c>
+      <c r="Q13">
+        <v>2.534601051</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.2889829388493897</v>
+      </c>
+      <c r="T13">
+        <v>1.460300021376887</v>
+      </c>
+      <c r="U13">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V13">
+        <v>0.3</v>
+      </c>
+      <c r="W13">
+        <v>0.0371</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>6.919727640464743</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.260568031246352</v>
+      </c>
+      <c r="C14">
+        <v>65.5815289273946</v>
+      </c>
+      <c r="D14">
+        <v>45.7970089273946</v>
+      </c>
+      <c r="E14">
+        <v>7.986479999999999</v>
+      </c>
+      <c r="F14">
+        <v>8.715479999999999</v>
+      </c>
+      <c r="G14">
+        <v>28.5</v>
+      </c>
+      <c r="H14">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>3.71</v>
+      </c>
+      <c r="K14">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L14">
+        <v>2.93</v>
+      </c>
+      <c r="M14">
+        <v>0.46192044</v>
+      </c>
+      <c r="N14">
+        <v>2.46807956</v>
+      </c>
+      <c r="O14">
+        <v>0.7404238680000002</v>
+      </c>
+      <c r="P14">
+        <v>1.727655692</v>
+      </c>
+      <c r="Q14">
+        <v>2.507655692</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.2910409445981272</v>
+      </c>
+      <c r="T14">
+        <v>1.472312454569561</v>
+      </c>
+      <c r="U14">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V14">
+        <v>0.3</v>
+      </c>
+      <c r="W14">
+        <v>0.0371</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>6.343083670426015</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.2600422469167472</v>
+      </c>
+      <c r="C15">
+        <v>64.96407595997933</v>
+      </c>
+      <c r="D15">
+        <v>45.90584595997932</v>
+      </c>
+      <c r="E15">
+        <v>8.712770000000003</v>
+      </c>
+      <c r="F15">
+        <v>9.441770000000002</v>
+      </c>
+      <c r="G15">
+        <v>28.5</v>
+      </c>
+      <c r="H15">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>3.71</v>
+      </c>
+      <c r="K15">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L15">
+        <v>2.93</v>
+      </c>
+      <c r="M15">
+        <v>0.5192973500000001</v>
+      </c>
+      <c r="N15">
+        <v>2.41070265</v>
+      </c>
+      <c r="O15">
+        <v>0.7232107950000002</v>
+      </c>
+      <c r="P15">
+        <v>1.687491855</v>
+      </c>
+      <c r="Q15">
+        <v>2.467491855</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.2931462608238473</v>
+      </c>
+      <c r="T15">
+        <v>1.484601035651723</v>
+      </c>
+      <c r="U15">
+        <v>0.055</v>
+      </c>
+      <c r="V15">
+        <v>0.3</v>
+      </c>
+      <c r="W15">
+        <v>0.0385</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>5.642239460686637</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.2593484625871423</v>
+      </c>
+      <c r="C16">
+        <v>64.38219302675589</v>
+      </c>
+      <c r="D16">
+        <v>46.05025302675588</v>
+      </c>
+      <c r="E16">
+        <v>9.439060000000003</v>
+      </c>
+      <c r="F16">
+        <v>10.16806</v>
+      </c>
+      <c r="G16">
+        <v>28.5</v>
+      </c>
+      <c r="H16">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>3.71</v>
+      </c>
+      <c r="K16">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L16">
+        <v>2.93</v>
+      </c>
+      <c r="M16">
+        <v>0.5592433000000001</v>
+      </c>
+      <c r="N16">
+        <v>2.3707567</v>
+      </c>
+      <c r="O16">
+        <v>0.7112270100000002</v>
+      </c>
+      <c r="P16">
+        <v>1.65952969</v>
+      </c>
+      <c r="Q16">
+        <v>2.43952969</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.2953005378920259</v>
+      </c>
+      <c r="T16">
+        <v>1.497175397689283</v>
+      </c>
+      <c r="U16">
+        <v>0.055</v>
+      </c>
+      <c r="V16">
+        <v>0.3</v>
+      </c>
+      <c r="W16">
+        <v>0.0385</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>5.239222356351878</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.2586546782575375</v>
+      </c>
+      <c r="C17">
+        <v>63.80122148974021</v>
+      </c>
+      <c r="D17">
+        <v>46.19557148974022</v>
+      </c>
+      <c r="E17">
+        <v>10.16535</v>
+      </c>
+      <c r="F17">
+        <v>10.89435</v>
+      </c>
+      <c r="G17">
+        <v>28.5</v>
+      </c>
+      <c r="H17">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>3.71</v>
+      </c>
+      <c r="K17">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L17">
+        <v>2.93</v>
+      </c>
+      <c r="M17">
+        <v>0.5991892500000001</v>
+      </c>
+      <c r="N17">
+        <v>2.33081075</v>
+      </c>
+      <c r="O17">
+        <v>0.6992432250000001</v>
+      </c>
+      <c r="P17">
+        <v>1.631567525</v>
+      </c>
+      <c r="Q17">
+        <v>2.411567525</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.297505503832397</v>
+      </c>
+      <c r="T17">
+        <v>1.510045627068903</v>
+      </c>
+      <c r="U17">
+        <v>0.055</v>
+      </c>
+      <c r="V17">
+        <v>0.3</v>
+      </c>
+      <c r="W17">
+        <v>0.0385</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>4.889940865928418</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.2579608939279326</v>
+      </c>
+      <c r="C18">
+        <v>63.22117000438717</v>
+      </c>
+      <c r="D18">
+        <v>46.34181000438717</v>
+      </c>
+      <c r="E18">
+        <v>10.89164</v>
+      </c>
+      <c r="F18">
+        <v>11.62064</v>
+      </c>
+      <c r="G18">
+        <v>28.5</v>
+      </c>
+      <c r="H18">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>3.71</v>
+      </c>
+      <c r="K18">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L18">
+        <v>2.93</v>
+      </c>
+      <c r="M18">
+        <v>0.6391352000000001</v>
+      </c>
+      <c r="N18">
+        <v>2.2908648</v>
+      </c>
+      <c r="O18">
+        <v>0.6872594400000002</v>
+      </c>
+      <c r="P18">
+        <v>1.60360536</v>
+      </c>
+      <c r="Q18">
+        <v>2.38360536</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.2997629689618246</v>
+      </c>
+      <c r="T18">
+        <v>1.523222290481372</v>
+      </c>
+      <c r="U18">
+        <v>0.055</v>
+      </c>
+      <c r="V18">
+        <v>0.3</v>
+      </c>
+      <c r="W18">
+        <v>0.0385</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>4.584319561807892</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.2577193095983278</v>
+      </c>
+      <c r="C19">
+        <v>62.54601964630878</v>
+      </c>
+      <c r="D19">
+        <v>46.39294964630878</v>
+      </c>
+      <c r="E19">
+        <v>11.61793</v>
+      </c>
+      <c r="F19">
+        <v>12.34693</v>
+      </c>
+      <c r="G19">
+        <v>28.5</v>
+      </c>
+      <c r="H19">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>3.71</v>
+      </c>
+      <c r="K19">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L19">
+        <v>2.93</v>
+      </c>
+      <c r="M19">
+        <v>0.7259994840000001</v>
+      </c>
+      <c r="N19">
+        <v>2.204000516</v>
+      </c>
+      <c r="O19">
+        <v>0.6612001548000001</v>
+      </c>
+      <c r="P19">
+        <v>1.5428003612</v>
+      </c>
+      <c r="Q19">
+        <v>2.3228003612</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.3020748308413589</v>
+      </c>
+      <c r="T19">
+        <v>1.536716463855587</v>
+      </c>
+      <c r="U19">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V19">
+        <v>0.3</v>
+      </c>
+      <c r="W19">
+        <v>0.04116</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>4.035815540607188</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.257581325268723</v>
+      </c>
+      <c r="C20">
+        <v>61.84898945652099</v>
+      </c>
+      <c r="D20">
+        <v>46.42220945652098</v>
+      </c>
+      <c r="E20">
+        <v>12.34422</v>
+      </c>
+      <c r="F20">
+        <v>13.07322</v>
+      </c>
+      <c r="G20">
+        <v>28.5</v>
+      </c>
+      <c r="H20">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>3.71</v>
+      </c>
+      <c r="K20">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L20">
+        <v>2.93</v>
+      </c>
+      <c r="M20">
+        <v>0.8236128600000001</v>
+      </c>
+      <c r="N20">
+        <v>2.10638714</v>
+      </c>
+      <c r="O20">
+        <v>0.631916142</v>
+      </c>
+      <c r="P20">
+        <v>1.474470998</v>
+      </c>
+      <c r="Q20">
+        <v>2.254470998</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.3044430795960036</v>
+      </c>
+      <c r="T20">
+        <v>1.55053976340966</v>
+      </c>
+      <c r="U20">
+        <v>0.063</v>
+      </c>
+      <c r="V20">
+        <v>0.3</v>
+      </c>
+      <c r="W20">
+        <v>0.0441</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>3.55749666172041</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.2578878409391182</v>
+      </c>
+      <c r="C21">
+        <v>61.05775228924873</v>
+      </c>
+      <c r="D21">
+        <v>46.35726228924872</v>
+      </c>
+      <c r="E21">
+        <v>13.07051</v>
+      </c>
+      <c r="F21">
+        <v>13.79951</v>
+      </c>
+      <c r="G21">
+        <v>28.5</v>
+      </c>
+      <c r="H21">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>3.71</v>
+      </c>
+      <c r="K21">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L21">
+        <v>2.93</v>
+      </c>
+      <c r="M21">
+        <v>0.967345651</v>
+      </c>
+      <c r="N21">
+        <v>1.962654349</v>
+      </c>
+      <c r="O21">
+        <v>0.5887963047000001</v>
+      </c>
+      <c r="P21">
+        <v>1.3738580443</v>
+      </c>
+      <c r="Q21">
+        <v>2.1538580443</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.3068698036285409</v>
+      </c>
+      <c r="T21">
+        <v>1.564704379002106</v>
+      </c>
+      <c r="U21">
+        <v>0.0701</v>
+      </c>
+      <c r="V21">
+        <v>0.3</v>
+      </c>
+      <c r="W21">
+        <v>0.04907</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>3.028906985802947</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.2602817566095134</v>
+      </c>
+      <c r="C22">
+        <v>59.83040351885748</v>
+      </c>
+      <c r="D22">
+        <v>45.85620351885749</v>
+      </c>
+      <c r="E22">
+        <v>13.7968</v>
+      </c>
+      <c r="F22">
+        <v>14.5258</v>
+      </c>
+      <c r="G22">
+        <v>28.5</v>
+      </c>
+      <c r="H22">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>3.71</v>
+      </c>
+      <c r="K22">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L22">
+        <v>2.93</v>
+      </c>
+      <c r="M22">
+        <v>1.32765812</v>
+      </c>
+      <c r="N22">
+        <v>1.60234188</v>
+      </c>
+      <c r="O22">
+        <v>0.480702564</v>
+      </c>
+      <c r="P22">
+        <v>1.121639316</v>
+      </c>
+      <c r="Q22">
+        <v>1.901639316</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.3093571957618917</v>
+      </c>
+      <c r="T22">
+        <v>1.579223109984364</v>
+      </c>
+      <c r="U22">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V22">
+        <v>0.3</v>
+      </c>
+      <c r="W22">
+        <v>0.06398000000000001</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>2.206893443321086</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.2598427722799085</v>
+      </c>
+      <c r="C23">
+        <v>59.19518256650071</v>
+      </c>
+      <c r="D23">
+        <v>45.94727256650071</v>
+      </c>
+      <c r="E23">
+        <v>14.52309</v>
+      </c>
+      <c r="F23">
+        <v>15.25209</v>
+      </c>
+      <c r="G23">
+        <v>28.5</v>
+      </c>
+      <c r="H23">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>3.71</v>
+      </c>
+      <c r="K23">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L23">
+        <v>2.93</v>
+      </c>
+      <c r="M23">
+        <v>1.394041026</v>
+      </c>
+      <c r="N23">
+        <v>1.535958974</v>
+      </c>
+      <c r="O23">
+        <v>0.4607876922</v>
+      </c>
+      <c r="P23">
+        <v>1.0751712818</v>
+      </c>
+      <c r="Q23">
+        <v>1.8551712818</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.3119075598479855</v>
+      </c>
+      <c r="T23">
+        <v>1.594109403776298</v>
+      </c>
+      <c r="U23">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V23">
+        <v>0.3</v>
+      </c>
+      <c r="W23">
+        <v>0.06398000000000001</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>2.101803279353415</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.2594037879503037</v>
+      </c>
+      <c r="C24">
+        <v>58.56032405474569</v>
+      </c>
+      <c r="D24">
+        <v>46.03870405474569</v>
+      </c>
+      <c r="E24">
+        <v>15.24938</v>
+      </c>
+      <c r="F24">
+        <v>15.97838</v>
+      </c>
+      <c r="G24">
+        <v>28.5</v>
+      </c>
+      <c r="H24">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>3.71</v>
+      </c>
+      <c r="K24">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L24">
+        <v>2.93</v>
+      </c>
+      <c r="M24">
+        <v>1.460423932</v>
+      </c>
+      <c r="N24">
+        <v>1.469576068</v>
+      </c>
+      <c r="O24">
+        <v>0.4408728204</v>
+      </c>
+      <c r="P24">
+        <v>1.0287032476</v>
+      </c>
+      <c r="Q24">
+        <v>1.8087032476</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.3145233178850047</v>
+      </c>
+      <c r="T24">
+        <v>1.609377397409051</v>
+      </c>
+      <c r="U24">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V24">
+        <v>0.3</v>
+      </c>
+      <c r="W24">
+        <v>0.06398000000000001</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>2.006266766655533</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.2623619036206988</v>
+      </c>
+      <c r="C25">
+        <v>57.22486133925438</v>
+      </c>
+      <c r="D25">
+        <v>45.42953133925438</v>
+      </c>
+      <c r="E25">
+        <v>15.97567</v>
+      </c>
+      <c r="F25">
+        <v>16.70467</v>
+      </c>
+      <c r="G25">
+        <v>28.5</v>
+      </c>
+      <c r="H25">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>3.71</v>
+      </c>
+      <c r="K25">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L25">
+        <v>2.93</v>
+      </c>
+      <c r="M25">
+        <v>1.879275375</v>
+      </c>
+      <c r="N25">
+        <v>1.050724625</v>
+      </c>
+      <c r="O25">
+        <v>0.3152173875000001</v>
+      </c>
+      <c r="P25">
+        <v>0.7355072375</v>
+      </c>
+      <c r="Q25">
+        <v>1.5155072375</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.3172070176892193</v>
+      </c>
+      <c r="T25">
+        <v>1.625041962304993</v>
+      </c>
+      <c r="U25">
+        <v>0.1125</v>
+      </c>
+      <c r="V25">
+        <v>0.3</v>
+      </c>
+      <c r="W25">
+        <v>0.07875</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>1.559111580440945</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.2806560532849171</v>
+      </c>
+      <c r="C26">
+        <v>53.06225194923877</v>
+      </c>
+      <c r="D26">
+        <v>41.99321194923876</v>
+      </c>
+      <c r="E26">
+        <v>16.70196</v>
+      </c>
+      <c r="F26">
+        <v>17.43096</v>
+      </c>
+      <c r="G26">
+        <v>28.5</v>
+      </c>
+      <c r="H26">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>3.71</v>
+      </c>
+      <c r="K26">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L26">
+        <v>2.93</v>
+      </c>
+      <c r="M26">
+        <v>3.426926736</v>
+      </c>
+      <c r="N26">
+        <v>-0.4969267359999994</v>
+      </c>
+      <c r="O26">
+        <v>-0.1490780207999998</v>
+      </c>
+      <c r="P26">
+        <v>-0.3478487151999995</v>
+      </c>
+      <c r="Q26">
+        <v>0.4321512848000003</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.3231245485895919</v>
+      </c>
+      <c r="T26">
+        <v>1.659582169323325</v>
+      </c>
+      <c r="U26">
+        <v>0.1966</v>
+      </c>
+      <c r="V26">
+        <v>0.2564980426240429</v>
+      </c>
+      <c r="W26">
+        <v>0.1461724848201132</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>0.8549934754134763</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.282234053284917</v>
+      </c>
+      <c r="C27">
+        <v>52.06375151868596</v>
+      </c>
+      <c r="D27">
+        <v>41.72100151868597</v>
+      </c>
+      <c r="E27">
+        <v>17.42825</v>
+      </c>
+      <c r="F27">
+        <v>18.15725</v>
+      </c>
+      <c r="G27">
+        <v>28.5</v>
+      </c>
+      <c r="H27">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>3.71</v>
+      </c>
+      <c r="K27">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L27">
+        <v>2.93</v>
+      </c>
+      <c r="M27">
+        <v>3.56971535</v>
+      </c>
+      <c r="N27">
+        <v>-0.6397153499999999</v>
+      </c>
+      <c r="O27">
+        <v>-0.191914605</v>
+      </c>
+      <c r="P27">
+        <v>-0.4478007449999999</v>
+      </c>
+      <c r="Q27">
+        <v>0.3321992549999999</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.3269155425707865</v>
+      </c>
+      <c r="T27">
+        <v>1.68170993158097</v>
+      </c>
+      <c r="U27">
+        <v>0.1966</v>
+      </c>
+      <c r="V27">
+        <v>0.2462381209190812</v>
+      </c>
+      <c r="W27">
+        <v>0.1481895854273086</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>0.8207937363969371</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.2894244009177727</v>
+      </c>
+      <c r="C28">
+        <v>50.14049704351232</v>
+      </c>
+      <c r="D28">
+        <v>40.52403704351232</v>
+      </c>
+      <c r="E28">
+        <v>18.15454</v>
+      </c>
+      <c r="F28">
+        <v>18.88354</v>
+      </c>
+      <c r="G28">
+        <v>28.5</v>
+      </c>
+      <c r="H28">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>3.71</v>
+      </c>
+      <c r="K28">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L28">
+        <v>2.93</v>
+      </c>
+      <c r="M28">
+        <v>4.037300852</v>
+      </c>
+      <c r="N28">
+        <v>-1.107300852</v>
+      </c>
+      <c r="O28">
+        <v>-0.3321902556000002</v>
+      </c>
+      <c r="P28">
+        <v>-0.7751105964000001</v>
+      </c>
+      <c r="Q28">
+        <v>0.004889403599999675</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.33235000616344</v>
+      </c>
+      <c r="T28">
+        <v>1.713430509079266</v>
+      </c>
+      <c r="U28">
+        <v>0.2138</v>
+      </c>
+      <c r="V28">
+        <v>0.2177197172622299</v>
+      </c>
+      <c r="W28">
+        <v>0.1672515244493352</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>0.7257323908740998</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.2911744009177727</v>
+      </c>
+      <c r="C29">
+        <v>49.13320760550175</v>
+      </c>
+      <c r="D29">
+        <v>40.24303760550175</v>
+      </c>
+      <c r="E29">
+        <v>18.88083</v>
+      </c>
+      <c r="F29">
+        <v>19.60983</v>
+      </c>
+      <c r="G29">
+        <v>28.5</v>
+      </c>
+      <c r="H29">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>3.71</v>
+      </c>
+      <c r="K29">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L29">
+        <v>2.93</v>
+      </c>
+      <c r="M29">
+        <v>4.192581654</v>
+      </c>
+      <c r="N29">
+        <v>-1.262581654</v>
+      </c>
+      <c r="O29">
+        <v>-0.3787744962000001</v>
+      </c>
+      <c r="P29">
+        <v>-0.8838071578000002</v>
+      </c>
+      <c r="Q29">
+        <v>-0.1038071578000004</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.336371239124583</v>
+      </c>
+      <c r="T29">
+        <v>1.736902159888571</v>
+      </c>
+      <c r="U29">
+        <v>0.2138</v>
+      </c>
+      <c r="V29">
+        <v>0.2096560240302955</v>
+      </c>
+      <c r="W29">
+        <v>0.1689755420623228</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>0.6988534134343183</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.2929244009177728</v>
+      </c>
+      <c r="C30">
+        <v>48.12978831152097</v>
+      </c>
+      <c r="D30">
+        <v>39.96590831152098</v>
+      </c>
+      <c r="E30">
+        <v>19.60712000000001</v>
+      </c>
+      <c r="F30">
+        <v>20.33612</v>
+      </c>
+      <c r="G30">
+        <v>28.5</v>
+      </c>
+      <c r="H30">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>3.71</v>
+      </c>
+      <c r="K30">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L30">
+        <v>2.93</v>
+      </c>
+      <c r="M30">
+        <v>4.347862456000001</v>
+      </c>
+      <c r="N30">
+        <v>-1.417862456</v>
+      </c>
+      <c r="O30">
+        <v>-0.4253587368000002</v>
+      </c>
+      <c r="P30">
+        <v>-0.9925037192000001</v>
+      </c>
+      <c r="Q30">
+        <v>-0.2125037192000003</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.3405041730013134</v>
+      </c>
+      <c r="T30">
+        <v>1.761025800998135</v>
+      </c>
+      <c r="U30">
+        <v>0.2138</v>
+      </c>
+      <c r="V30">
+        <v>0.2021683088863564</v>
+      </c>
+      <c r="W30">
+        <v>0.170576415560097</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>0.6738943629545211</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.2946744009177727</v>
+      </c>
+      <c r="C31">
+        <v>47.13015975442306</v>
+      </c>
+      <c r="D31">
+        <v>39.69256975442305</v>
+      </c>
+      <c r="E31">
+        <v>20.33341</v>
+      </c>
+      <c r="F31">
+        <v>21.06241</v>
+      </c>
+      <c r="G31">
+        <v>28.5</v>
+      </c>
+      <c r="H31">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>3.71</v>
+      </c>
+      <c r="K31">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L31">
+        <v>2.93</v>
+      </c>
+      <c r="M31">
+        <v>4.503143258</v>
+      </c>
+      <c r="N31">
+        <v>-1.573143258</v>
+      </c>
+      <c r="O31">
+        <v>-0.4719429773999999</v>
+      </c>
+      <c r="P31">
+        <v>-1.1012002806</v>
+      </c>
+      <c r="Q31">
+        <v>-0.3212002805999998</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.3447535275506276</v>
+      </c>
+      <c r="T31">
+        <v>1.785828981293883</v>
+      </c>
+      <c r="U31">
+        <v>0.2138</v>
+      </c>
+      <c r="V31">
+        <v>0.1951969878902752</v>
+      </c>
+      <c r="W31">
+        <v>0.1720668839890592</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>0.650656626300917</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.2964244009177727</v>
+      </c>
+      <c r="C32">
+        <v>46.13424468465954</v>
+      </c>
+      <c r="D32">
+        <v>39.42294468465953</v>
+      </c>
+      <c r="E32">
+        <v>21.0597</v>
+      </c>
+      <c r="F32">
+        <v>21.7887</v>
+      </c>
+      <c r="G32">
+        <v>28.5</v>
+      </c>
+      <c r="H32">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>3.71</v>
+      </c>
+      <c r="K32">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L32">
+        <v>2.93</v>
+      </c>
+      <c r="M32">
+        <v>4.658424060000001</v>
+      </c>
+      <c r="N32">
+        <v>-1.72842406</v>
+      </c>
+      <c r="O32">
+        <v>-0.5185272180000002</v>
+      </c>
+      <c r="P32">
+        <v>-1.209896842</v>
+      </c>
+      <c r="Q32">
+        <v>-0.4298968420000004</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.3491242922299223</v>
+      </c>
+      <c r="T32">
+        <v>1.811340823883796</v>
+      </c>
+      <c r="U32">
+        <v>0.2138</v>
+      </c>
+      <c r="V32">
+        <v>0.188690421627266</v>
+      </c>
+      <c r="W32">
+        <v>0.1734579878560905</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>0.6289680720908863</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.2981744009177728</v>
+      </c>
+      <c r="C33">
+        <v>45.1419679374939</v>
+      </c>
+      <c r="D33">
+        <v>39.15695793749389</v>
+      </c>
+      <c r="E33">
+        <v>21.78599</v>
+      </c>
+      <c r="F33">
+        <v>22.51499</v>
+      </c>
+      <c r="G33">
+        <v>28.5</v>
+      </c>
+      <c r="H33">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>3.71</v>
+      </c>
+      <c r="K33">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L33">
+        <v>2.93</v>
+      </c>
+      <c r="M33">
+        <v>4.813704862</v>
+      </c>
+      <c r="N33">
+        <v>-1.883704862</v>
+      </c>
+      <c r="O33">
+        <v>-0.5651114586</v>
+      </c>
+      <c r="P33">
+        <v>-1.3185934034</v>
+      </c>
+      <c r="Q33">
+        <v>-0.5385934033999997</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.3536217457405009</v>
+      </c>
+      <c r="T33">
+        <v>1.837592140171967</v>
+      </c>
+      <c r="U33">
+        <v>0.2138</v>
+      </c>
+      <c r="V33">
+        <v>0.182603633832838</v>
+      </c>
+      <c r="W33">
+        <v>0.1747593430865392</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>0.6086787794427935</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.2999244009177727</v>
+      </c>
+      <c r="C34">
+        <v>44.15325636314169</v>
+      </c>
+      <c r="D34">
+        <v>38.8945363631417</v>
+      </c>
+      <c r="E34">
+        <v>22.51228</v>
+      </c>
+      <c r="F34">
+        <v>23.24128</v>
+      </c>
+      <c r="G34">
+        <v>28.5</v>
+      </c>
+      <c r="H34">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>3.71</v>
+      </c>
+      <c r="K34">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L34">
+        <v>2.93</v>
+      </c>
+      <c r="M34">
+        <v>4.968985664000001</v>
+      </c>
+      <c r="N34">
+        <v>-2.038985664000001</v>
+      </c>
+      <c r="O34">
+        <v>-0.6116956992000002</v>
+      </c>
+      <c r="P34">
+        <v>-1.4272899648</v>
+      </c>
+      <c r="Q34">
+        <v>-0.6472899648000006</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.3582514772955082</v>
+      </c>
+      <c r="T34">
+        <v>1.864615553998025</v>
+      </c>
+      <c r="U34">
+        <v>0.2138</v>
+      </c>
+      <c r="V34">
+        <v>0.1768972702755618</v>
+      </c>
+      <c r="W34">
+        <v>0.1759793636150849</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>0.589657567585206</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.3016744009177727</v>
+      </c>
+      <c r="C35">
+        <v>43.1680387597012</v>
+      </c>
+      <c r="D35">
+        <v>38.63560875970121</v>
+      </c>
+      <c r="E35">
+        <v>23.23857</v>
+      </c>
+      <c r="F35">
+        <v>23.96757</v>
+      </c>
+      <c r="G35">
+        <v>28.5</v>
+      </c>
+      <c r="H35">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>3.71</v>
+      </c>
+      <c r="K35">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L35">
+        <v>2.93</v>
+      </c>
+      <c r="M35">
+        <v>5.124266466</v>
+      </c>
+      <c r="N35">
+        <v>-2.194266466</v>
+      </c>
+      <c r="O35">
+        <v>-0.6582799398</v>
+      </c>
+      <c r="P35">
+        <v>-1.5359865262</v>
+      </c>
+      <c r="Q35">
+        <v>-0.7559865262000001</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.3630194097924561</v>
+      </c>
+      <c r="T35">
+        <v>1.892445636893518</v>
+      </c>
+      <c r="U35">
+        <v>0.2138</v>
+      </c>
+      <c r="V35">
+        <v>0.1715367469338782</v>
+      </c>
+      <c r="W35">
+        <v>0.1771254435055368</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>0.5717891564462605</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.3034244009177727</v>
+      </c>
+      <c r="C36">
+        <v>42.18624580874511</v>
+      </c>
+      <c r="D36">
+        <v>38.38010580874511</v>
+      </c>
+      <c r="E36">
+        <v>23.96486000000001</v>
+      </c>
+      <c r="F36">
+        <v>24.69386</v>
+      </c>
+      <c r="G36">
+        <v>28.5</v>
+      </c>
+      <c r="H36">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>3.71</v>
+      </c>
+      <c r="K36">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L36">
+        <v>2.93</v>
+      </c>
+      <c r="M36">
+        <v>5.279547268000001</v>
+      </c>
+      <c r="N36">
+        <v>-2.349547268000001</v>
+      </c>
+      <c r="O36">
+        <v>-0.7048641804000003</v>
+      </c>
+      <c r="P36">
+        <v>-1.6446830876</v>
+      </c>
+      <c r="Q36">
+        <v>-0.8646830876000005</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.3679318250923418</v>
+      </c>
+      <c r="T36">
+        <v>1.921119055634329</v>
+      </c>
+      <c r="U36">
+        <v>0.2138</v>
+      </c>
+      <c r="V36">
+        <v>0.1664915484946464</v>
+      </c>
+      <c r="W36">
+        <v>0.1782041069318446</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>0.554971828315488</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.3051744009177728</v>
+      </c>
+      <c r="C37">
+        <v>41.20781001345136</v>
+      </c>
+      <c r="D37">
+        <v>38.12796001345138</v>
+      </c>
+      <c r="E37">
+        <v>24.69115</v>
+      </c>
+      <c r="F37">
+        <v>25.42015</v>
+      </c>
+      <c r="G37">
+        <v>28.5</v>
+      </c>
+      <c r="H37">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>3.71</v>
+      </c>
+      <c r="K37">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L37">
+        <v>2.93</v>
+      </c>
+      <c r="M37">
+        <v>5.43482807</v>
+      </c>
+      <c r="N37">
+        <v>-2.50482807</v>
+      </c>
+      <c r="O37">
+        <v>-0.7514484210000001</v>
+      </c>
+      <c r="P37">
+        <v>-1.753379649</v>
+      </c>
+      <c r="Q37">
+        <v>-0.973379649</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.3729953916322241</v>
+      </c>
+      <c r="T37">
+        <v>1.950674733413319</v>
+      </c>
+      <c r="U37">
+        <v>0.2138</v>
+      </c>
+      <c r="V37">
+        <v>0.1617346471090851</v>
+      </c>
+      <c r="W37">
+        <v>0.1792211324480776</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>0.5391154903636171</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.3069244009177727</v>
+      </c>
+      <c r="C38">
+        <v>40.23266563915665</v>
+      </c>
+      <c r="D38">
+        <v>37.87910563915666</v>
+      </c>
+      <c r="E38">
+        <v>25.41744</v>
+      </c>
+      <c r="F38">
+        <v>26.14644</v>
+      </c>
+      <c r="G38">
+        <v>28.5</v>
+      </c>
+      <c r="H38">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>3.71</v>
+      </c>
+      <c r="K38">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L38">
+        <v>2.93</v>
+      </c>
+      <c r="M38">
+        <v>5.590108872</v>
+      </c>
+      <c r="N38">
+        <v>-2.660108872</v>
+      </c>
+      <c r="O38">
+        <v>-0.7980326616000001</v>
+      </c>
+      <c r="P38">
+        <v>-1.8620762104</v>
+      </c>
+      <c r="Q38">
+        <v>-1.0820762104</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.3782171946264775</v>
+      </c>
+      <c r="T38">
+        <v>1.981154026122902</v>
+      </c>
+      <c r="U38">
+        <v>0.2138</v>
+      </c>
+      <c r="V38">
+        <v>0.1572420180227216</v>
+      </c>
+      <c r="W38">
+        <v>0.1801816565467421</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>0.5241400600757388</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.3086744009177728</v>
+      </c>
+      <c r="C39">
+        <v>39.26074865622276</v>
+      </c>
+      <c r="D39">
+        <v>37.63347865622276</v>
+      </c>
+      <c r="E39">
+        <v>26.14373</v>
+      </c>
+      <c r="F39">
+        <v>26.87273</v>
+      </c>
+      <c r="G39">
+        <v>28.5</v>
+      </c>
+      <c r="H39">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>3.71</v>
+      </c>
+      <c r="K39">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L39">
+        <v>2.93</v>
+      </c>
+      <c r="M39">
+        <v>5.745389674</v>
+      </c>
+      <c r="N39">
+        <v>-2.815389674</v>
+      </c>
+      <c r="O39">
+        <v>-0.8446169022000001</v>
+      </c>
+      <c r="P39">
+        <v>-1.9707727718</v>
+      </c>
+      <c r="Q39">
+        <v>-1.1907727718</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.3836047691443581</v>
+      </c>
+      <c r="T39">
+        <v>2.01260091542644</v>
+      </c>
+      <c r="U39">
+        <v>0.2138</v>
+      </c>
+      <c r="V39">
+        <v>0.1529922337518373</v>
+      </c>
+      <c r="W39">
+        <v>0.1810902604238572</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>0.5099741125061241</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.3212889778273901</v>
+      </c>
+      <c r="C40">
+        <v>36.85393145641307</v>
+      </c>
+      <c r="D40">
+        <v>35.95295145641307</v>
+      </c>
+      <c r="E40">
+        <v>26.87002</v>
+      </c>
+      <c r="F40">
+        <v>27.59902</v>
+      </c>
+      <c r="G40">
+        <v>28.5</v>
+      </c>
+      <c r="H40">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>3.71</v>
+      </c>
+      <c r="K40">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L40">
+        <v>2.93</v>
+      </c>
+      <c r="M40">
+        <v>6.590645976000001</v>
+      </c>
+      <c r="N40">
+        <v>-3.660645976000001</v>
+      </c>
+      <c r="O40">
+        <v>-1.098193792800001</v>
+      </c>
+      <c r="P40">
+        <v>-2.5624521832</v>
+      </c>
+      <c r="Q40">
+        <v>-1.782452183200001</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.3913670668880047</v>
+      </c>
+      <c r="T40">
+        <v>2.05790889531153</v>
+      </c>
+      <c r="U40">
+        <v>0.2388</v>
+      </c>
+      <c r="V40">
+        <v>0.1333708415231072</v>
+      </c>
+      <c r="W40">
+        <v>0.206951043044282</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>0.4445694717436905</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.3232889778273901</v>
+      </c>
+      <c r="C41">
+        <v>35.87488683842413</v>
+      </c>
+      <c r="D41">
+        <v>35.70019683842413</v>
+      </c>
+      <c r="E41">
+        <v>27.59631</v>
+      </c>
+      <c r="F41">
+        <v>28.32531</v>
+      </c>
+      <c r="G41">
+        <v>28.5</v>
+      </c>
+      <c r="H41">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>3.71</v>
+      </c>
+      <c r="K41">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L41">
+        <v>2.93</v>
+      </c>
+      <c r="M41">
+        <v>6.764084028000001</v>
+      </c>
+      <c r="N41">
+        <v>-3.834084028000001</v>
+      </c>
+      <c r="O41">
+        <v>-1.1502252084</v>
+      </c>
+      <c r="P41">
+        <v>-2.6838588196</v>
+      </c>
+      <c r="Q41">
+        <v>-1.9038588196</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.3971468548697752</v>
+      </c>
+      <c r="T41">
+        <v>2.09164510671008</v>
+      </c>
+      <c r="U41">
+        <v>0.2388</v>
+      </c>
+      <c r="V41">
+        <v>0.129951076355848</v>
+      </c>
+      <c r="W41">
+        <v>0.2077676829662235</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.4331702545194933</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.32528897782739</v>
+      </c>
+      <c r="C42">
+        <v>34.89937121648811</v>
+      </c>
+      <c r="D42">
+        <v>35.45097121648811</v>
+      </c>
+      <c r="E42">
+        <v>28.3226</v>
+      </c>
+      <c r="F42">
+        <v>29.0516</v>
+      </c>
+      <c r="G42">
+        <v>28.5</v>
+      </c>
+      <c r="H42">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>3.71</v>
+      </c>
+      <c r="K42">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L42">
+        <v>2.93</v>
+      </c>
+      <c r="M42">
+        <v>6.937522080000002</v>
+      </c>
+      <c r="N42">
+        <v>-4.007522080000001</v>
+      </c>
+      <c r="O42">
+        <v>-1.202256624000001</v>
+      </c>
+      <c r="P42">
+        <v>-2.805265456000001</v>
+      </c>
+      <c r="Q42">
+        <v>-2.025265456000001</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.4031193024509381</v>
+      </c>
+      <c r="T42">
+        <v>2.126505858488581</v>
+      </c>
+      <c r="U42">
+        <v>0.2388</v>
+      </c>
+      <c r="V42">
+        <v>0.1267022994469518</v>
+      </c>
+      <c r="W42">
+        <v>0.2085434908920679</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.4223409981565061</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.32728897782739</v>
+      </c>
+      <c r="C43">
+        <v>33.92731119446877</v>
+      </c>
+      <c r="D43">
+        <v>35.20520119446877</v>
+      </c>
+      <c r="E43">
+        <v>29.04889</v>
+      </c>
+      <c r="F43">
+        <v>29.77789</v>
+      </c>
+      <c r="G43">
+        <v>28.5</v>
+      </c>
+      <c r="H43">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>3.71</v>
+      </c>
+      <c r="K43">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L43">
+        <v>2.93</v>
+      </c>
+      <c r="M43">
+        <v>7.110960132000001</v>
+      </c>
+      <c r="N43">
+        <v>-4.180960132000001</v>
+      </c>
+      <c r="O43">
+        <v>-1.2542880396</v>
+      </c>
+      <c r="P43">
+        <v>-2.9266720924</v>
+      </c>
+      <c r="Q43">
+        <v>-2.146672092400001</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.40929420588231</v>
+      </c>
+      <c r="T43">
+        <v>2.162548330666354</v>
+      </c>
+      <c r="U43">
+        <v>0.2388</v>
+      </c>
+      <c r="V43">
+        <v>0.1236119994604408</v>
+      </c>
+      <c r="W43">
+        <v>0.2092814545288467</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.4120399982014692</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.3292889778273901</v>
+      </c>
+      <c r="C44">
+        <v>32.95863539754266</v>
+      </c>
+      <c r="D44">
+        <v>34.96281539754267</v>
+      </c>
+      <c r="E44">
+        <v>29.77518</v>
+      </c>
+      <c r="F44">
+        <v>30.50418</v>
+      </c>
+      <c r="G44">
+        <v>28.5</v>
+      </c>
+      <c r="H44">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>3.71</v>
+      </c>
+      <c r="K44">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L44">
+        <v>2.93</v>
+      </c>
+      <c r="M44">
+        <v>7.284398184</v>
+      </c>
+      <c r="N44">
+        <v>-4.354398184000001</v>
+      </c>
+      <c r="O44">
+        <v>-1.3063194552</v>
+      </c>
+      <c r="P44">
+        <v>-3.0480787288</v>
+      </c>
+      <c r="Q44">
+        <v>-2.2680787288</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.4156820370182118</v>
+      </c>
+      <c r="T44">
+        <v>2.199833646712325</v>
+      </c>
+      <c r="U44">
+        <v>0.2388</v>
+      </c>
+      <c r="V44">
+        <v>0.1206688566161446</v>
+      </c>
+      <c r="W44">
+        <v>0.2099842770400647</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.4022295220538152</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.33128897782739</v>
+      </c>
+      <c r="C45">
+        <v>31.9932744030919</v>
+      </c>
+      <c r="D45">
+        <v>34.7237444030919</v>
+      </c>
+      <c r="E45">
+        <v>30.50147</v>
+      </c>
+      <c r="F45">
+        <v>31.23047</v>
+      </c>
+      <c r="G45">
+        <v>28.5</v>
+      </c>
+      <c r="H45">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>3.71</v>
+      </c>
+      <c r="K45">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L45">
+        <v>2.93</v>
+      </c>
+      <c r="M45">
+        <v>7.457836236</v>
+      </c>
+      <c r="N45">
+        <v>-4.527836236000001</v>
+      </c>
+      <c r="O45">
+        <v>-1.3583508708</v>
+      </c>
+      <c r="P45">
+        <v>-3.1694853652</v>
+      </c>
+      <c r="Q45">
+        <v>-2.3894853652</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.4222940025799348</v>
+      </c>
+      <c r="T45">
+        <v>2.238427219461664</v>
+      </c>
+      <c r="U45">
+        <v>0.2388</v>
+      </c>
+      <c r="V45">
+        <v>0.1178626041366994</v>
+      </c>
+      <c r="W45">
+        <v>0.2106544101321562</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.3928753471223312</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.33328897782739</v>
+      </c>
+      <c r="C46">
+        <v>31.03116067441268</v>
+      </c>
+      <c r="D46">
+        <v>34.48792067441268</v>
+      </c>
+      <c r="E46">
+        <v>31.22776</v>
+      </c>
+      <c r="F46">
+        <v>31.95676</v>
+      </c>
+      <c r="G46">
+        <v>28.5</v>
+      </c>
+      <c r="H46">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>3.71</v>
+      </c>
+      <c r="K46">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L46">
+        <v>2.93</v>
+      </c>
+      <c r="M46">
+        <v>7.631274288000001</v>
+      </c>
+      <c r="N46">
+        <v>-4.701274288</v>
+      </c>
+      <c r="O46">
+        <v>-1.4103822864</v>
+      </c>
+      <c r="P46">
+        <v>-3.2908920016</v>
+      </c>
+      <c r="Q46">
+        <v>-2.5108920016</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.4291421097688622</v>
+      </c>
+      <c r="T46">
+        <v>2.278399134094908</v>
+      </c>
+      <c r="U46">
+        <v>0.2388</v>
+      </c>
+      <c r="V46">
+        <v>0.115183908588138</v>
+      </c>
+      <c r="W46">
+        <v>0.2112940826291527</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.3839463619604601</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.33528897782739</v>
+      </c>
+      <c r="C47">
+        <v>30.07222849710726</v>
+      </c>
+      <c r="D47">
+        <v>34.25527849710726</v>
+      </c>
+      <c r="E47">
+        <v>31.95405</v>
+      </c>
+      <c r="F47">
+        <v>32.68305</v>
+      </c>
+      <c r="G47">
+        <v>28.5</v>
+      </c>
+      <c r="H47">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>3.71</v>
+      </c>
+      <c r="K47">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L47">
+        <v>2.93</v>
+      </c>
+      <c r="M47">
+        <v>7.804712340000001</v>
+      </c>
+      <c r="N47">
+        <v>-4.87471234</v>
+      </c>
+      <c r="O47">
+        <v>-1.462413702</v>
+      </c>
+      <c r="P47">
+        <v>-3.412298638</v>
+      </c>
+      <c r="Q47">
+        <v>-2.632298638</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.436239239037387</v>
+      </c>
+      <c r="T47">
+        <v>2.319824572896633</v>
+      </c>
+      <c r="U47">
+        <v>0.2388</v>
+      </c>
+      <c r="V47">
+        <v>0.1126242661750683</v>
+      </c>
+      <c r="W47">
+        <v>0.2119053252373937</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.375414220583561</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.3372889778273901</v>
+      </c>
+      <c r="C48">
+        <v>29.11641391803273</v>
+      </c>
+      <c r="D48">
+        <v>34.02575391803273</v>
+      </c>
+      <c r="E48">
+        <v>32.68034</v>
+      </c>
+      <c r="F48">
+        <v>33.40934</v>
+      </c>
+      <c r="G48">
+        <v>28.5</v>
+      </c>
+      <c r="H48">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>3.71</v>
+      </c>
+      <c r="K48">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L48">
+        <v>2.93</v>
+      </c>
+      <c r="M48">
+        <v>7.978150392000001</v>
+      </c>
+      <c r="N48">
+        <v>-5.048150392</v>
+      </c>
+      <c r="O48">
+        <v>-1.5144451176</v>
+      </c>
+      <c r="P48">
+        <v>-3.5337052744</v>
+      </c>
+      <c r="Q48">
+        <v>-2.7537052744</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.4435992249454868</v>
+      </c>
+      <c r="T48">
+        <v>2.362784287209534</v>
+      </c>
+      <c r="U48">
+        <v>0.2388</v>
+      </c>
+      <c r="V48">
+        <v>0.1101759125625668</v>
+      </c>
+      <c r="W48">
+        <v>0.2124899920800591</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.3672530418752227</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.3392889778273901</v>
+      </c>
+      <c r="C49">
+        <v>28.16365468668823</v>
+      </c>
+      <c r="D49">
+        <v>33.79928468668823</v>
+      </c>
+      <c r="E49">
+        <v>33.40663000000001</v>
+      </c>
+      <c r="F49">
+        <v>34.13563000000001</v>
+      </c>
+      <c r="G49">
+        <v>28.5</v>
+      </c>
+      <c r="H49">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>3.71</v>
+      </c>
+      <c r="K49">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L49">
+        <v>2.93</v>
+      </c>
+      <c r="M49">
+        <v>8.151588444000001</v>
+      </c>
+      <c r="N49">
+        <v>-5.221588444000002</v>
+      </c>
+      <c r="O49">
+        <v>-1.566476533200001</v>
+      </c>
+      <c r="P49">
+        <v>-3.655111910800001</v>
+      </c>
+      <c r="Q49">
+        <v>-2.875111910800001</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.4512369461708734</v>
+      </c>
+      <c r="T49">
+        <v>2.407365122817262</v>
+      </c>
+      <c r="U49">
+        <v>0.2388</v>
+      </c>
+      <c r="V49">
+        <v>0.1078317442101718</v>
+      </c>
+      <c r="W49">
+        <v>0.213049779482611</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.3594391473672391</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.34128897782739</v>
+      </c>
+      <c r="C50">
+        <v>27.21389019892707</v>
+      </c>
+      <c r="D50">
+        <v>33.57581019892707</v>
+      </c>
+      <c r="E50">
+        <v>34.13292</v>
+      </c>
+      <c r="F50">
+        <v>34.86192</v>
+      </c>
+      <c r="G50">
+        <v>28.5</v>
+      </c>
+      <c r="H50">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>3.71</v>
+      </c>
+      <c r="K50">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L50">
+        <v>2.93</v>
+      </c>
+      <c r="M50">
+        <v>8.325026496</v>
+      </c>
+      <c r="N50">
+        <v>-5.395026496</v>
+      </c>
+      <c r="O50">
+        <v>-1.6185079488</v>
+      </c>
+      <c r="P50">
+        <v>-3.776518547199999</v>
+      </c>
+      <c r="Q50">
+        <v>-2.9965185472</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.4591684259049286</v>
+      </c>
+      <c r="T50">
+        <v>2.453660605948362</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>0.1055852495391265</v>
+      </c>
+      <c r="W50">
+        <v>0.2135862424100566</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.3519508317970883</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.3432889778273901</v>
+      </c>
+      <c r="C51">
+        <v>26.26706144288735</v>
+      </c>
+      <c r="D51">
+        <v>33.35527144288735</v>
+      </c>
+      <c r="E51">
+        <v>34.85921</v>
+      </c>
+      <c r="F51">
+        <v>35.58821</v>
+      </c>
+      <c r="G51">
+        <v>28.5</v>
+      </c>
+      <c r="H51">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>3.71</v>
+      </c>
+      <c r="K51">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L51">
+        <v>2.93</v>
+      </c>
+      <c r="M51">
+        <v>8.498464548000001</v>
+      </c>
+      <c r="N51">
+        <v>-5.568464548000001</v>
+      </c>
+      <c r="O51">
+        <v>-1.670539364400001</v>
+      </c>
+      <c r="P51">
+        <v>-3.897925183600001</v>
+      </c>
+      <c r="Q51">
+        <v>-3.117925183600001</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.4674109440599272</v>
+      </c>
+      <c r="T51">
+        <v>2.50177159822186</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>0.1034304485281239</v>
+      </c>
+      <c r="W51">
+        <v>0.214100808891484</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.344768161760413</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.34528897782739</v>
+      </c>
+      <c r="C52">
+        <v>25.32311094703962</v>
+      </c>
+      <c r="D52">
+        <v>33.13761094703963</v>
+      </c>
+      <c r="E52">
+        <v>35.5855</v>
+      </c>
+      <c r="F52">
+        <v>36.3145</v>
+      </c>
+      <c r="G52">
+        <v>28.5</v>
+      </c>
+      <c r="H52">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>3.71</v>
+      </c>
+      <c r="K52">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L52">
+        <v>2.93</v>
+      </c>
+      <c r="M52">
+        <v>8.671902600000001</v>
+      </c>
+      <c r="N52">
+        <v>-5.741902600000001</v>
+      </c>
+      <c r="O52">
+        <v>-1.722570780000001</v>
+      </c>
+      <c r="P52">
+        <v>-4.019331820000001</v>
+      </c>
+      <c r="Q52">
+        <v>-3.239331820000001</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.4759831629411257</v>
+      </c>
+      <c r="T52">
+        <v>2.551807030186297</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>0.1013618395575615</v>
+      </c>
+      <c r="W52">
+        <v>0.2145947927136543</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.3378727985252048</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.34728897782739</v>
+      </c>
+      <c r="C53">
+        <v>24.38198273025522</v>
+      </c>
+      <c r="D53">
+        <v>32.92277273025523</v>
+      </c>
+      <c r="E53">
+        <v>36.31179</v>
+      </c>
+      <c r="F53">
+        <v>37.04079</v>
+      </c>
+      <c r="G53">
+        <v>28.5</v>
+      </c>
+      <c r="H53">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>3.71</v>
+      </c>
+      <c r="K53">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L53">
+        <v>2.93</v>
+      </c>
+      <c r="M53">
+        <v>8.845340652000001</v>
+      </c>
+      <c r="N53">
+        <v>-5.915340652000001</v>
+      </c>
+      <c r="O53">
+        <v>-1.774602195600001</v>
+      </c>
+      <c r="P53">
+        <v>-4.1407384564</v>
+      </c>
+      <c r="Q53">
+        <v>-3.3607384564</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.4849052683072712</v>
+      </c>
+      <c r="T53">
+        <v>2.603884724679895</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>0.09937435250741319</v>
+      </c>
+      <c r="W53">
+        <v>0.2150694046212297</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.3312478416913772</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.3492889778273901</v>
+      </c>
+      <c r="C54">
+        <v>23.44362225380462</v>
+      </c>
+      <c r="D54">
+        <v>32.71070225380463</v>
+      </c>
+      <c r="E54">
+        <v>37.03808000000001</v>
+      </c>
+      <c r="F54">
+        <v>37.76708000000001</v>
+      </c>
+      <c r="G54">
+        <v>28.5</v>
+      </c>
+      <c r="H54">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>3.71</v>
+      </c>
+      <c r="K54">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L54">
+        <v>2.93</v>
+      </c>
+      <c r="M54">
+        <v>9.018778704000002</v>
+      </c>
+      <c r="N54">
+        <v>-6.088778704000003</v>
+      </c>
+      <c r="O54">
+        <v>-1.826633611200001</v>
+      </c>
+      <c r="P54">
+        <v>-4.262145092800002</v>
+      </c>
+      <c r="Q54">
+        <v>-3.482145092800002</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.4941991280636727</v>
+      </c>
+      <c r="T54">
+        <v>2.658132323110726</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>0.09746330726688601</v>
+      </c>
+      <c r="W54">
+        <v>0.2155257622246676</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.3248776908896199</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.35128897782739</v>
+      </c>
+      <c r="C55">
+        <v>22.50797637519907</v>
+      </c>
+      <c r="D55">
+        <v>32.50134637519908</v>
+      </c>
+      <c r="E55">
+        <v>37.76437000000001</v>
+      </c>
+      <c r="F55">
+        <v>38.49337000000001</v>
+      </c>
+      <c r="G55">
+        <v>28.5</v>
+      </c>
+      <c r="H55">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>3.71</v>
+      </c>
+      <c r="K55">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L55">
+        <v>2.93</v>
+      </c>
+      <c r="M55">
+        <v>9.192216756000002</v>
+      </c>
+      <c r="N55">
+        <v>-6.262216756000003</v>
+      </c>
+      <c r="O55">
+        <v>-1.878665026800001</v>
+      </c>
+      <c r="P55">
+        <v>-4.383551729200001</v>
+      </c>
+      <c r="Q55">
+        <v>-3.603551729200002</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.5038884712139635</v>
+      </c>
+      <c r="T55">
+        <v>2.714688329985422</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>0.0956243769410957</v>
+      </c>
+      <c r="W55">
+        <v>0.2159648987864664</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.3187479231369856</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.35328897782739</v>
+      </c>
+      <c r="C56">
+        <v>21.57499330379332</v>
+      </c>
+      <c r="D56">
+        <v>32.29465330379332</v>
+      </c>
+      <c r="E56">
+        <v>38.49066000000001</v>
+      </c>
+      <c r="F56">
+        <v>39.21966</v>
+      </c>
+      <c r="G56">
+        <v>28.5</v>
+      </c>
+      <c r="H56">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>3.71</v>
+      </c>
+      <c r="K56">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L56">
+        <v>2.93</v>
+      </c>
+      <c r="M56">
+        <v>9.365654808000002</v>
+      </c>
+      <c r="N56">
+        <v>-6.435654808000002</v>
+      </c>
+      <c r="O56">
+        <v>-1.930696442400001</v>
+      </c>
+      <c r="P56">
+        <v>-4.504958365600001</v>
+      </c>
+      <c r="Q56">
+        <v>-3.724958365600001</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.5139990901533975</v>
+      </c>
+      <c r="T56">
+        <v>2.773703293680758</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>0.09385355514589024</v>
+      </c>
+      <c r="W56">
+        <v>0.2163877710311614</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.312845183819634</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.3552889778273901</v>
+      </c>
+      <c r="C57">
+        <v>20.64462255807202</v>
+      </c>
+      <c r="D57">
+        <v>32.09057255807202</v>
+      </c>
+      <c r="E57">
+        <v>39.21695</v>
+      </c>
+      <c r="F57">
+        <v>39.94595</v>
+      </c>
+      <c r="G57">
+        <v>28.5</v>
+      </c>
+      <c r="H57">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>3.71</v>
+      </c>
+      <c r="K57">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L57">
+        <v>2.93</v>
+      </c>
+      <c r="M57">
+        <v>9.539092860000002</v>
+      </c>
+      <c r="N57">
+        <v>-6.609092860000002</v>
+      </c>
+      <c r="O57">
+        <v>-1.982727858000001</v>
+      </c>
+      <c r="P57">
+        <v>-4.626365002000002</v>
+      </c>
+      <c r="Q57">
+        <v>-3.846365002000002</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.5245590699345842</v>
+      </c>
+      <c r="T57">
+        <v>2.835341144651442</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>0.09214712687051042</v>
+      </c>
+      <c r="W57">
+        <v>0.2167952661033221</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.307157089568368</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.3572889778273901</v>
+      </c>
+      <c r="C58">
+        <v>19.7168149245452</v>
+      </c>
+      <c r="D58">
+        <v>31.88905492454521</v>
+      </c>
+      <c r="E58">
+        <v>39.94324000000001</v>
+      </c>
+      <c r="F58">
+        <v>40.67224000000001</v>
+      </c>
+      <c r="G58">
+        <v>28.5</v>
+      </c>
+      <c r="H58">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>3.71</v>
+      </c>
+      <c r="K58">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L58">
+        <v>2.93</v>
+      </c>
+      <c r="M58">
+        <v>9.712530912000002</v>
+      </c>
+      <c r="N58">
+        <v>-6.782530912000002</v>
+      </c>
+      <c r="O58">
+        <v>-2.034759273600001</v>
+      </c>
+      <c r="P58">
+        <v>-4.747771638400001</v>
+      </c>
+      <c r="Q58">
+        <v>-3.967771638400002</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.5355990487967339</v>
+      </c>
+      <c r="T58">
+        <v>2.899780716120792</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>0.09050164246210844</v>
+      </c>
+      <c r="W58">
+        <v>0.2171882077800485</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.3016721415403614</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.3592889778273901</v>
+      </c>
+      <c r="C59">
+        <v>18.79152241818307</v>
+      </c>
+      <c r="D59">
+        <v>31.69005241818308</v>
+      </c>
+      <c r="E59">
+        <v>40.66953000000001</v>
+      </c>
+      <c r="F59">
+        <v>41.39853000000001</v>
+      </c>
+      <c r="G59">
+        <v>28.5</v>
+      </c>
+      <c r="H59">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>3.71</v>
+      </c>
+      <c r="K59">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L59">
+        <v>2.93</v>
+      </c>
+      <c r="M59">
+        <v>9.885968964000002</v>
+      </c>
+      <c r="N59">
+        <v>-6.955968964000002</v>
+      </c>
+      <c r="O59">
+        <v>-2.086790689200001</v>
+      </c>
+      <c r="P59">
+        <v>-4.869178274800001</v>
+      </c>
+      <c r="Q59">
+        <v>-4.089178274800002</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.5471525150478207</v>
+      </c>
+      <c r="T59">
+        <v>2.967217476960811</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>0.08891389434873812</v>
+      </c>
+      <c r="W59">
+        <v>0.2175673620295213</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.296379647829127</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.36128897782739</v>
+      </c>
+      <c r="C60">
+        <v>17.86869824432276</v>
+      </c>
+      <c r="D60">
+        <v>31.49351824432276</v>
+      </c>
+      <c r="E60">
+        <v>41.39582</v>
+      </c>
+      <c r="F60">
+        <v>42.12482</v>
+      </c>
+      <c r="G60">
+        <v>28.5</v>
+      </c>
+      <c r="H60">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>3.71</v>
+      </c>
+      <c r="K60">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L60">
+        <v>2.93</v>
+      </c>
+      <c r="M60">
+        <v>10.059407016</v>
+      </c>
+      <c r="N60">
+        <v>-7.129407016</v>
+      </c>
+      <c r="O60">
+        <v>-2.1388221048</v>
+      </c>
+      <c r="P60">
+        <v>-4.990584911199999</v>
+      </c>
+      <c r="Q60">
+        <v>-4.2105849112</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.5592561463584829</v>
+      </c>
+      <c r="T60">
+        <v>3.037865512126543</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>0.08738089617031161</v>
+      </c>
+      <c r="W60">
+        <v>0.2179334419945296</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.2912696539010386</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.36328897782739</v>
+      </c>
+      <c r="C61">
+        <v>16.94829676198406</v>
+      </c>
+      <c r="D61">
+        <v>31.29940676198406</v>
+      </c>
+      <c r="E61">
+        <v>42.12211</v>
+      </c>
+      <c r="F61">
+        <v>42.85111</v>
+      </c>
+      <c r="G61">
+        <v>28.5</v>
+      </c>
+      <c r="H61">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>3.71</v>
+      </c>
+      <c r="K61">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L61">
+        <v>2.93</v>
+      </c>
+      <c r="M61">
+        <v>10.232845068</v>
+      </c>
+      <c r="N61">
+        <v>-7.302845068</v>
+      </c>
+      <c r="O61">
+        <v>-2.1908535204</v>
+      </c>
+      <c r="P61">
+        <v>-5.1119915476</v>
+      </c>
+      <c r="Q61">
+        <v>-4.331991547599999</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.5719501987086899</v>
+      </c>
+      <c r="T61">
+        <v>3.111959792910118</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>0.08589986403183175</v>
+      </c>
+      <c r="W61">
+        <v>0.2182871124691986</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.2863328801061058</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.36528897782739</v>
+      </c>
+      <c r="C62">
+        <v>16.03027344853339</v>
+      </c>
+      <c r="D62">
+        <v>31.10767344853339</v>
+      </c>
+      <c r="E62">
+        <v>42.84840000000001</v>
+      </c>
+      <c r="F62">
+        <v>43.5774</v>
+      </c>
+      <c r="G62">
+        <v>28.5</v>
+      </c>
+      <c r="H62">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>3.71</v>
+      </c>
+      <c r="K62">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L62">
+        <v>2.93</v>
+      </c>
+      <c r="M62">
+        <v>10.40628312</v>
+      </c>
+      <c r="N62">
+        <v>-7.476283120000002</v>
+      </c>
+      <c r="O62">
+        <v>-2.242884936000001</v>
+      </c>
+      <c r="P62">
+        <v>-5.233398184</v>
+      </c>
+      <c r="Q62">
+        <v>-4.453398184000001</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.5852789536764071</v>
+      </c>
+      <c r="T62">
+        <v>3.189758787732871</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>0.08446819963130121</v>
+      </c>
+      <c r="W62">
+        <v>0.2186289939280453</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.2815606654376707</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.3672889778273901</v>
+      </c>
+      <c r="C63">
+        <v>15.11458486563858</v>
+      </c>
+      <c r="D63">
+        <v>30.91827486563858</v>
+      </c>
+      <c r="E63">
+        <v>43.57469</v>
+      </c>
+      <c r="F63">
+        <v>44.30369</v>
+      </c>
+      <c r="G63">
+        <v>28.5</v>
+      </c>
+      <c r="H63">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>3.71</v>
+      </c>
+      <c r="K63">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L63">
+        <v>2.93</v>
+      </c>
+      <c r="M63">
+        <v>10.579721172</v>
+      </c>
+      <c r="N63">
+        <v>-7.649721172000001</v>
+      </c>
+      <c r="O63">
+        <v>-2.294916351600001</v>
+      </c>
+      <c r="P63">
+        <v>-5.3548048204</v>
+      </c>
+      <c r="Q63">
+        <v>-4.574804820400001</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.5992912345399048</v>
+      </c>
+      <c r="T63">
+        <v>3.271547474597817</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0.08308347504718153</v>
+      </c>
+      <c r="W63">
+        <v>0.2189596661587331</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.2769449168239383</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.36928897782739</v>
+      </c>
+      <c r="C64">
+        <v>14.20118862645995</v>
+      </c>
+      <c r="D64">
+        <v>30.73116862645995</v>
+      </c>
+      <c r="E64">
+        <v>44.30098</v>
+      </c>
+      <c r="F64">
+        <v>45.02998</v>
+      </c>
+      <c r="G64">
+        <v>28.5</v>
+      </c>
+      <c r="H64">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>3.71</v>
+      </c>
+      <c r="K64">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L64">
+        <v>2.93</v>
+      </c>
+      <c r="M64">
+        <v>10.753159224</v>
+      </c>
+      <c r="N64">
+        <v>-7.823159224000001</v>
+      </c>
+      <c r="O64">
+        <v>-2.346947767200001</v>
+      </c>
+      <c r="P64">
+        <v>-5.476211456800001</v>
+      </c>
+      <c r="Q64">
+        <v>-4.6962114568</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.6140410038699022</v>
+      </c>
+      <c r="T64">
+        <v>3.357640829192496</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0.08174341899803345</v>
+      </c>
+      <c r="W64">
+        <v>0.2192796715432696</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.272478063326778</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.37128897782739</v>
+      </c>
+      <c r="C65">
+        <v>13.29004336402527</v>
+      </c>
+      <c r="D65">
+        <v>30.54631336402527</v>
+      </c>
+      <c r="E65">
+        <v>45.02727</v>
+      </c>
+      <c r="F65">
+        <v>45.75627</v>
+      </c>
+      <c r="G65">
+        <v>28.5</v>
+      </c>
+      <c r="H65">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>3.71</v>
+      </c>
+      <c r="K65">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L65">
+        <v>2.93</v>
+      </c>
+      <c r="M65">
+        <v>10.926597276</v>
+      </c>
+      <c r="N65">
+        <v>-7.996597276000001</v>
+      </c>
+      <c r="O65">
+        <v>-2.398979182800001</v>
+      </c>
+      <c r="P65">
+        <v>-5.5976180932</v>
+      </c>
+      <c r="Q65">
+        <v>-4.8176180932</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.6295880580285482</v>
+      </c>
+      <c r="T65">
+        <v>3.448387878630131</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0.08044590441076307</v>
+      </c>
+      <c r="W65">
+        <v>0.2195895180267098</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.2681530147025435</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.3732889778273901</v>
+      </c>
+      <c r="C66">
+        <v>12.38110870073959</v>
+      </c>
+      <c r="D66">
+        <v>30.36366870073959</v>
+      </c>
+      <c r="E66">
+        <v>45.75356000000001</v>
+      </c>
+      <c r="F66">
+        <v>46.48256000000001</v>
+      </c>
+      <c r="G66">
+        <v>28.5</v>
+      </c>
+      <c r="H66">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>3.71</v>
+      </c>
+      <c r="K66">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L66">
+        <v>2.93</v>
+      </c>
+      <c r="M66">
+        <v>11.100035328</v>
+      </c>
+      <c r="N66">
+        <v>-8.170035328000003</v>
+      </c>
+      <c r="O66">
+        <v>-2.451010598400001</v>
+      </c>
+      <c r="P66">
+        <v>-5.719024729600001</v>
+      </c>
+      <c r="Q66">
+        <v>-4.939024729600002</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.6459988374182304</v>
+      </c>
+      <c r="T66">
+        <v>3.544176430814302</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0.07918893715434489</v>
+      </c>
+      <c r="W66">
+        <v>0.2198896818075425</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.2639631238478162</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.3752889778273901</v>
+      </c>
+      <c r="C67">
+        <v>11.47434521898224</v>
+      </c>
+      <c r="D67">
+        <v>30.18319521898225</v>
+      </c>
+      <c r="E67">
+        <v>46.47985000000001</v>
+      </c>
+      <c r="F67">
+        <v>47.20885000000001</v>
+      </c>
+      <c r="G67">
+        <v>28.5</v>
+      </c>
+      <c r="H67">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>3.71</v>
+      </c>
+      <c r="K67">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L67">
+        <v>2.93</v>
+      </c>
+      <c r="M67">
+        <v>11.27347338</v>
+      </c>
+      <c r="N67">
+        <v>-8.343473380000002</v>
+      </c>
+      <c r="O67">
+        <v>-2.503042014000001</v>
+      </c>
+      <c r="P67">
+        <v>-5.840431366000002</v>
+      </c>
+      <c r="Q67">
+        <v>-5.060431366000001</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.6633473756301798</v>
+      </c>
+      <c r="T67">
+        <v>3.645438614551853</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0.07797064581350881</v>
+      </c>
+      <c r="W67">
+        <v>0.2201806097797341</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.2599021527116959</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.37728897782739</v>
+      </c>
+      <c r="C68">
+        <v>10.56971443274623</v>
+      </c>
+      <c r="D68">
+        <v>30.00485443274624</v>
+      </c>
+      <c r="E68">
+        <v>47.20614</v>
+      </c>
+      <c r="F68">
+        <v>47.93514</v>
+      </c>
+      <c r="G68">
+        <v>28.5</v>
+      </c>
+      <c r="H68">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>3.71</v>
+      </c>
+      <c r="K68">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L68">
+        <v>2.93</v>
+      </c>
+      <c r="M68">
+        <v>11.446911432</v>
+      </c>
+      <c r="N68">
+        <v>-8.516911432000002</v>
+      </c>
+      <c r="O68">
+        <v>-2.555073429600001</v>
+      </c>
+      <c r="P68">
+        <v>-5.961838002400001</v>
+      </c>
+      <c r="Q68">
+        <v>-5.181838002400001</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.6817164160898908</v>
+      </c>
+      <c r="T68">
+        <v>3.75265739733279</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0.076789272392092</v>
+      </c>
+      <c r="W68">
+        <v>0.2204627217527684</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.2559642413069733</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.3792889778273901</v>
+      </c>
+      <c r="C69">
+        <v>9.66717876027716</v>
+      </c>
+      <c r="D69">
+        <v>29.82860876027717</v>
+      </c>
+      <c r="E69">
+        <v>47.93243</v>
+      </c>
+      <c r="F69">
+        <v>48.66143</v>
+      </c>
+      <c r="G69">
+        <v>28.5</v>
+      </c>
+      <c r="H69">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>3.71</v>
+      </c>
+      <c r="K69">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L69">
+        <v>2.93</v>
+      </c>
+      <c r="M69">
+        <v>11.620349484</v>
+      </c>
+      <c r="N69">
+        <v>-8.690349484000002</v>
+      </c>
+      <c r="O69">
+        <v>-2.607104845200001</v>
+      </c>
+      <c r="P69">
+        <v>-6.083244638800001</v>
+      </c>
+      <c r="Q69">
+        <v>-5.303244638800001</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.7011987317289785</v>
+      </c>
+      <c r="T69">
+        <v>3.866374288161057</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.07564316384892646</v>
+      </c>
+      <c r="W69">
+        <v>0.2207364124728764</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.2521438794964215</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.38128897782739</v>
+      </c>
+      <c r="C70">
+        <v>8.766701497670944</v>
+      </c>
+      <c r="D70">
+        <v>29.65442149767096</v>
+      </c>
+      <c r="E70">
+        <v>48.65872000000001</v>
+      </c>
+      <c r="F70">
+        <v>49.38772000000001</v>
+      </c>
+      <c r="G70">
+        <v>28.5</v>
+      </c>
+      <c r="H70">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>3.71</v>
+      </c>
+      <c r="K70">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L70">
+        <v>2.93</v>
+      </c>
+      <c r="M70">
+        <v>11.793787536</v>
+      </c>
+      <c r="N70">
+        <v>-8.863787536000004</v>
+      </c>
+      <c r="O70">
+        <v>-2.659136260800001</v>
+      </c>
+      <c r="P70">
+        <v>-6.204651275200002</v>
+      </c>
+      <c r="Q70">
+        <v>-5.424651275200002</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.7218986920955091</v>
+      </c>
+      <c r="T70">
+        <v>3.98719848466609</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.07453076438055989</v>
+      </c>
+      <c r="W70">
+        <v>0.2210020534659223</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.2484358812685329</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.3832889778273901</v>
+      </c>
+      <c r="C71">
+        <v>7.868246793391023</v>
+      </c>
+      <c r="D71">
+        <v>29.48225679339103</v>
+      </c>
+      <c r="E71">
+        <v>49.38501000000001</v>
+      </c>
+      <c r="F71">
+        <v>50.11401000000001</v>
+      </c>
+      <c r="G71">
+        <v>28.5</v>
+      </c>
+      <c r="H71">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>3.71</v>
+      </c>
+      <c r="K71">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L71">
+        <v>2.93</v>
+      </c>
+      <c r="M71">
+        <v>11.967225588</v>
+      </c>
+      <c r="N71">
+        <v>-9.037225588000002</v>
+      </c>
+      <c r="O71">
+        <v>-2.711167676400001</v>
+      </c>
+      <c r="P71">
+        <v>-6.326057911600001</v>
+      </c>
+      <c r="Q71">
+        <v>-5.546057911600002</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.7439341337760095</v>
+      </c>
+      <c r="T71">
+        <v>4.11581779062306</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.07345060837504454</v>
+      </c>
+      <c r="W71">
+        <v>0.2212599947200394</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.2448353612501484</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.38528897782739</v>
+      </c>
+      <c r="C72">
+        <v>6.971779623668318</v>
+      </c>
+      <c r="D72">
+        <v>29.31207962366832</v>
+      </c>
+      <c r="E72">
+        <v>50.11130000000001</v>
+      </c>
+      <c r="F72">
+        <v>50.84030000000001</v>
+      </c>
+      <c r="G72">
+        <v>28.5</v>
+      </c>
+      <c r="H72">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>3.71</v>
+      </c>
+      <c r="K72">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L72">
+        <v>2.93</v>
+      </c>
+      <c r="M72">
+        <v>12.14066364</v>
+      </c>
+      <c r="N72">
+        <v>-9.210663640000002</v>
+      </c>
+      <c r="O72">
+        <v>-2.763199092000001</v>
+      </c>
+      <c r="P72">
+        <v>-6.447464548000001</v>
+      </c>
+      <c r="Q72">
+        <v>-5.667464548000002</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.7674386049018762</v>
+      </c>
+      <c r="T72">
+        <v>4.253011716977162</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.07240131396968676</v>
+      </c>
+      <c r="W72">
+        <v>0.2215105662240388</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.2413377132322891</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.3872889778273901</v>
+      </c>
+      <c r="C73">
+        <v>6.077265768748084</v>
+      </c>
+      <c r="D73">
+        <v>29.14385576874808</v>
+      </c>
+      <c r="E73">
+        <v>50.83759</v>
+      </c>
+      <c r="F73">
+        <v>51.56659</v>
+      </c>
+      <c r="G73">
+        <v>28.5</v>
+      </c>
+      <c r="H73">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>3.71</v>
+      </c>
+      <c r="K73">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L73">
+        <v>2.93</v>
+      </c>
+      <c r="M73">
+        <v>12.314101692</v>
+      </c>
+      <c r="N73">
+        <v>-9.384101692</v>
+      </c>
+      <c r="O73">
+        <v>-2.8152305076</v>
+      </c>
+      <c r="P73">
+        <v>-6.568871184399999</v>
+      </c>
+      <c r="Q73">
+        <v>-5.7888711844</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.7925640740364237</v>
+      </c>
+      <c r="T73">
+        <v>4.39966729342465</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.07138157715321231</v>
+      </c>
+      <c r="W73">
+        <v>0.2217540793758129</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.2379385905107076</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.38928897782739</v>
+      </c>
+      <c r="C74">
+        <v>5.184671789950208</v>
+      </c>
+      <c r="D74">
+        <v>28.97755178995021</v>
+      </c>
+      <c r="E74">
+        <v>51.56388</v>
+      </c>
+      <c r="F74">
+        <v>52.29288</v>
+      </c>
+      <c r="G74">
+        <v>28.5</v>
+      </c>
+      <c r="H74">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>3.71</v>
+      </c>
+      <c r="K74">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L74">
+        <v>2.93</v>
+      </c>
+      <c r="M74">
+        <v>12.487539744</v>
+      </c>
+      <c r="N74">
+        <v>-9.557539744000001</v>
+      </c>
+      <c r="O74">
+        <v>-2.867261923200001</v>
+      </c>
+      <c r="P74">
+        <v>-6.6902778208</v>
+      </c>
+      <c r="Q74">
+        <v>-5.910277820800001</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.8194842195377245</v>
+      </c>
+      <c r="T74">
+        <v>4.556798268189816</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.07039016635941768</v>
+      </c>
+      <c r="W74">
+        <v>0.2219908282733711</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.2346338878647255</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.39128897782739</v>
+      </c>
+      <c r="C75">
+        <v>4.29396500751033</v>
+      </c>
+      <c r="D75">
+        <v>28.81313500751033</v>
+      </c>
+      <c r="E75">
+        <v>52.29017</v>
+      </c>
+      <c r="F75">
+        <v>53.01917</v>
+      </c>
+      <c r="G75">
+        <v>28.5</v>
+      </c>
+      <c r="H75">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>3.71</v>
+      </c>
+      <c r="K75">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L75">
+        <v>2.93</v>
+      </c>
+      <c r="M75">
+        <v>12.660977796</v>
+      </c>
+      <c r="N75">
+        <v>-9.730977796000001</v>
+      </c>
+      <c r="O75">
+        <v>-2.919293338800001</v>
+      </c>
+      <c r="P75">
+        <v>-6.8116844572</v>
+      </c>
+      <c r="Q75">
+        <v>-6.031684457200001</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.8483984498909736</v>
+      </c>
+      <c r="T75">
+        <v>4.725568574419068</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.06942591750517908</v>
+      </c>
+      <c r="W75">
+        <v>0.2222210908997632</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.2314197250172636</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.39328897782739</v>
+      </c>
+      <c r="C76">
+        <v>3.405113479171135</v>
+      </c>
+      <c r="D76">
+        <v>28.65057347917114</v>
+      </c>
+      <c r="E76">
+        <v>53.01646</v>
+      </c>
+      <c r="F76">
+        <v>53.74546</v>
+      </c>
+      <c r="G76">
+        <v>28.5</v>
+      </c>
+      <c r="H76">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>3.71</v>
+      </c>
+      <c r="K76">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L76">
+        <v>2.93</v>
+      </c>
+      <c r="M76">
+        <v>12.834415848</v>
+      </c>
+      <c r="N76">
+        <v>-9.904415848000001</v>
+      </c>
+      <c r="O76">
+        <v>-2.971324754400001</v>
+      </c>
+      <c r="P76">
+        <v>-6.9330910936</v>
+      </c>
+      <c r="Q76">
+        <v>-6.153091093600001</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.8795368518098572</v>
+      </c>
+      <c r="T76">
+        <v>4.907321211896725</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.06848772943078478</v>
+      </c>
+      <c r="W76">
+        <v>0.2224451302119286</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.2282924314359491</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.39528897782739</v>
+      </c>
+      <c r="C77">
+        <v>2.518085979494252</v>
+      </c>
+      <c r="D77">
+        <v>28.48983597949425</v>
+      </c>
+      <c r="E77">
+        <v>53.74275</v>
+      </c>
+      <c r="F77">
+        <v>54.47175</v>
+      </c>
+      <c r="G77">
+        <v>28.5</v>
+      </c>
+      <c r="H77">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>3.71</v>
+      </c>
+      <c r="K77">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L77">
+        <v>2.93</v>
+      </c>
+      <c r="M77">
+        <v>13.0078539</v>
+      </c>
+      <c r="N77">
+        <v>-10.0778539</v>
+      </c>
+      <c r="O77">
+        <v>-3.023356170000001</v>
+      </c>
+      <c r="P77">
+        <v>-7.05449773</v>
+      </c>
+      <c r="Q77">
+        <v>-6.27449773</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.9131663258822513</v>
+      </c>
+      <c r="T77">
+        <v>5.103614060372593</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.06757455970504098</v>
+      </c>
+      <c r="W77">
+        <v>0.2226631951424362</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.2252485323501365</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.3972889778273901</v>
+      </c>
+      <c r="C78">
+        <v>1.632851979864711</v>
+      </c>
+      <c r="D78">
+        <v>28.33089197986471</v>
+      </c>
+      <c r="E78">
+        <v>54.46904000000001</v>
+      </c>
+      <c r="F78">
+        <v>55.19804000000001</v>
+      </c>
+      <c r="G78">
+        <v>28.5</v>
+      </c>
+      <c r="H78">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>3.71</v>
+      </c>
+      <c r="K78">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L78">
+        <v>2.93</v>
+      </c>
+      <c r="M78">
+        <v>13.181291952</v>
+      </c>
+      <c r="N78">
+        <v>-10.251291952</v>
+      </c>
+      <c r="O78">
+        <v>-3.075387585600001</v>
+      </c>
+      <c r="P78">
+        <v>-7.175904366400001</v>
+      </c>
+      <c r="Q78">
+        <v>-6.395904366400002</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.9495982561273455</v>
+      </c>
+      <c r="T78">
+        <v>5.316264646221453</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.06668542076155359</v>
+      </c>
+      <c r="W78">
+        <v>0.222875521522141</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.2222847358718453</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.39928897782739</v>
+      </c>
+      <c r="C79">
+        <v>0.7493816291610074</v>
+      </c>
+      <c r="D79">
+        <v>28.17371162916101</v>
+      </c>
+      <c r="E79">
+        <v>55.19533000000001</v>
+      </c>
+      <c r="F79">
+        <v>55.92433</v>
+      </c>
+      <c r="G79">
+        <v>28.5</v>
+      </c>
+      <c r="H79">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>3.71</v>
+      </c>
+      <c r="K79">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L79">
+        <v>2.93</v>
+      </c>
+      <c r="M79">
+        <v>13.354730004</v>
+      </c>
+      <c r="N79">
+        <v>-10.424730004</v>
+      </c>
+      <c r="O79">
+        <v>-3.127419001200001</v>
+      </c>
+      <c r="P79">
+        <v>-7.297311002800001</v>
+      </c>
+      <c r="Q79">
+        <v>-6.517311002800001</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.9891981803067951</v>
+      </c>
+      <c r="T79">
+        <v>5.547406587361515</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.06581937633607887</v>
+      </c>
+      <c r="W79">
+        <v>0.2230823329309444</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.2193979211202628</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.40128897782739</v>
+      </c>
+      <c r="C80">
+        <v>-0.1323542649349889</v>
+      </c>
+      <c r="D80">
+        <v>28.01826573506502</v>
+      </c>
+      <c r="E80">
+        <v>55.92162</v>
+      </c>
+      <c r="F80">
+        <v>56.65062</v>
+      </c>
+      <c r="G80">
+        <v>28.5</v>
+      </c>
+      <c r="H80">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>3.71</v>
+      </c>
+      <c r="K80">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L80">
+        <v>2.93</v>
+      </c>
+      <c r="M80">
+        <v>13.528168056</v>
+      </c>
+      <c r="N80">
+        <v>-10.598168056</v>
+      </c>
+      <c r="O80">
+        <v>-3.179450416800001</v>
+      </c>
+      <c r="P80">
+        <v>-7.4187176392</v>
+      </c>
+      <c r="Q80">
+        <v>-6.638717639200001</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>1.032398097593468</v>
+      </c>
+      <c r="T80">
+        <v>5.799561432241584</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.06497553817792401</v>
+      </c>
+      <c r="W80">
+        <v>0.2232838414831118</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.2165851272597467</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.40328897782739</v>
+      </c>
+      <c r="C81">
+        <v>-1.012384254012701</v>
+      </c>
+      <c r="D81">
+        <v>27.8645257459873</v>
+      </c>
+      <c r="E81">
+        <v>56.64791000000001</v>
+      </c>
+      <c r="F81">
+        <v>57.37691000000001</v>
+      </c>
+      <c r="G81">
+        <v>28.5</v>
+      </c>
+      <c r="H81">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>3.71</v>
+      </c>
+      <c r="K81">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L81">
+        <v>2.93</v>
+      </c>
+      <c r="M81">
+        <v>13.701606108</v>
+      </c>
+      <c r="N81">
+        <v>-10.771606108</v>
+      </c>
+      <c r="O81">
+        <v>-3.231481832400001</v>
+      </c>
+      <c r="P81">
+        <v>-7.540124275600002</v>
+      </c>
+      <c r="Q81">
+        <v>-6.760124275600003</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>1.079712292716966</v>
+      </c>
+      <c r="T81">
+        <v>6.07573102425309</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.06415306301111484</v>
+      </c>
+      <c r="W81">
+        <v>0.2234802485529458</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.2138435433703827</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.40528897782739</v>
+      </c>
+      <c r="C82">
+        <v>-1.890736266415765</v>
+      </c>
+      <c r="D82">
+        <v>27.71246373358424</v>
+      </c>
+      <c r="E82">
+        <v>57.37420000000001</v>
+      </c>
+      <c r="F82">
+        <v>58.10320000000001</v>
+      </c>
+      <c r="G82">
+        <v>28.5</v>
+      </c>
+      <c r="H82">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>3.71</v>
+      </c>
+      <c r="K82">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L82">
+        <v>2.93</v>
+      </c>
+      <c r="M82">
+        <v>13.87504416</v>
+      </c>
+      <c r="N82">
+        <v>-10.94504416</v>
+      </c>
+      <c r="O82">
+        <v>-3.283513248000002</v>
+      </c>
+      <c r="P82">
+        <v>-7.661530912000002</v>
+      </c>
+      <c r="Q82">
+        <v>-6.881530912000002</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>1.131757907352815</v>
+      </c>
+      <c r="T82">
+        <v>6.379517575465743</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.0633511497234759</v>
+      </c>
+      <c r="W82">
+        <v>0.223671745446034</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.2111704990782529</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.4072889778273901</v>
+      </c>
+      <c r="C83">
+        <v>-2.767437624155569</v>
+      </c>
+      <c r="D83">
+        <v>27.56205237584444</v>
+      </c>
+      <c r="E83">
+        <v>58.10049000000001</v>
+      </c>
+      <c r="F83">
+        <v>58.82949000000001</v>
+      </c>
+      <c r="G83">
+        <v>28.5</v>
+      </c>
+      <c r="H83">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>3.71</v>
+      </c>
+      <c r="K83">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L83">
+        <v>2.93</v>
+      </c>
+      <c r="M83">
+        <v>14.048482212</v>
+      </c>
+      <c r="N83">
+        <v>-11.118482212</v>
+      </c>
+      <c r="O83">
+        <v>-3.335544663600002</v>
+      </c>
+      <c r="P83">
+        <v>-7.782937548400001</v>
+      </c>
+      <c r="Q83">
+        <v>-7.002937548400002</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>1.189282007739805</v>
+      </c>
+      <c r="T83">
+        <v>6.715281658384995</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.06256903676392682</v>
+      </c>
+      <c r="W83">
+        <v>0.2238585140207743</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.208563455879756</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.40928897782739</v>
+      </c>
+      <c r="C84">
+        <v>-3.642515059276974</v>
+      </c>
+      <c r="D84">
+        <v>27.41326494072303</v>
+      </c>
+      <c r="E84">
+        <v>58.82678000000001</v>
+      </c>
+      <c r="F84">
+        <v>59.55578000000001</v>
+      </c>
+      <c r="G84">
+        <v>28.5</v>
+      </c>
+      <c r="H84">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>3.71</v>
+      </c>
+      <c r="K84">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L84">
+        <v>2.93</v>
+      </c>
+      <c r="M84">
+        <v>14.221920264</v>
+      </c>
+      <c r="N84">
+        <v>-11.291920264</v>
+      </c>
+      <c r="O84">
+        <v>-3.387576079200001</v>
+      </c>
+      <c r="P84">
+        <v>-7.904344184800001</v>
+      </c>
+      <c r="Q84">
+        <v>-7.124344184800002</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>1.253197674836461</v>
+      </c>
+      <c r="T84">
+        <v>7.088352861628604</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.06180599973022041</v>
+      </c>
+      <c r="W84">
+        <v>0.2240407272644234</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.2060199991007347</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.41128897782739</v>
+      </c>
+      <c r="C85">
+        <v>-4.515994729696835</v>
+      </c>
+      <c r="D85">
+        <v>27.26607527030317</v>
+      </c>
+      <c r="E85">
+        <v>59.55307000000001</v>
+      </c>
+      <c r="F85">
+        <v>60.28207000000001</v>
+      </c>
+      <c r="G85">
+        <v>28.5</v>
+      </c>
+      <c r="H85">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>3.71</v>
+      </c>
+      <c r="K85">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L85">
+        <v>2.93</v>
+      </c>
+      <c r="M85">
+        <v>14.395358316</v>
+      </c>
+      <c r="N85">
+        <v>-11.465358316</v>
+      </c>
+      <c r="O85">
+        <v>-3.439607494800001</v>
+      </c>
+      <c r="P85">
+        <v>-8.025750821200003</v>
+      </c>
+      <c r="Q85">
+        <v>-7.245750821200003</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>1.324632832179782</v>
+      </c>
+      <c r="T85">
+        <v>7.505314794665582</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.06106134913106111</v>
+      </c>
+      <c r="W85">
+        <v>0.2242185498275026</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.2035378304368703</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.41328897782739</v>
+      </c>
+      <c r="C86">
+        <v>-5.387902234534963</v>
+      </c>
+      <c r="D86">
+        <v>27.12045776546504</v>
+      </c>
+      <c r="E86">
+        <v>60.27936</v>
+      </c>
+      <c r="F86">
+        <v>61.00836</v>
+      </c>
+      <c r="G86">
+        <v>28.5</v>
+      </c>
+      <c r="H86">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>3.71</v>
+      </c>
+      <c r="K86">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L86">
+        <v>2.93</v>
+      </c>
+      <c r="M86">
+        <v>14.568796368</v>
+      </c>
+      <c r="N86">
+        <v>-11.638796368</v>
+      </c>
+      <c r="O86">
+        <v>-3.491638910400001</v>
+      </c>
+      <c r="P86">
+        <v>-8.147157457600001</v>
+      </c>
+      <c r="Q86">
+        <v>-7.367157457600001</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>1.404997384191018</v>
+      </c>
+      <c r="T86">
+        <v>7.974396969332178</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.0603344283080723</v>
+      </c>
+      <c r="W86">
+        <v>0.2243921385200323</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.2011147610269076</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.41528897782739</v>
+      </c>
+      <c r="C87">
+        <v>-6.258262628956444</v>
+      </c>
+      <c r="D87">
+        <v>26.97638737104356</v>
+      </c>
+      <c r="E87">
+        <v>61.00565</v>
+      </c>
+      <c r="F87">
+        <v>61.73465</v>
+      </c>
+      <c r="G87">
+        <v>28.5</v>
+      </c>
+      <c r="H87">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>3.71</v>
+      </c>
+      <c r="K87">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L87">
+        <v>2.93</v>
+      </c>
+      <c r="M87">
+        <v>14.74223442</v>
+      </c>
+      <c r="N87">
+        <v>-11.81223442</v>
+      </c>
+      <c r="O87">
+        <v>-3.543670326000001</v>
+      </c>
+      <c r="P87">
+        <v>-8.268564094</v>
+      </c>
+      <c r="Q87">
+        <v>-7.488564094000001</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>1.496077209803752</v>
+      </c>
+      <c r="T87">
+        <v>8.506023433954324</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.05962461150444792</v>
+      </c>
+      <c r="W87">
+        <v>0.2245616427727379</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.1987487050148263</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.4172889778273901</v>
+      </c>
+      <c r="C88">
+        <v>-7.127100438543359</v>
+      </c>
+      <c r="D88">
+        <v>26.83383956145664</v>
+      </c>
+      <c r="E88">
+        <v>61.73194</v>
+      </c>
+      <c r="F88">
+        <v>62.46094</v>
+      </c>
+      <c r="G88">
+        <v>28.5</v>
+      </c>
+      <c r="H88">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>3.71</v>
+      </c>
+      <c r="K88">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L88">
+        <v>2.93</v>
+      </c>
+      <c r="M88">
+        <v>14.915672472</v>
+      </c>
+      <c r="N88">
+        <v>-11.985672472</v>
+      </c>
+      <c r="O88">
+        <v>-3.595701741600001</v>
+      </c>
+      <c r="P88">
+        <v>-8.3899707304</v>
+      </c>
+      <c r="Q88">
+        <v>-7.609970730400001</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>1.600168439075449</v>
+      </c>
+      <c r="T88">
+        <v>9.113596536379632</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.05893130206834968</v>
+      </c>
+      <c r="W88">
+        <v>0.2247272050660781</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.1964376735611656</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.4192889778273901</v>
+      </c>
+      <c r="C89">
+        <v>-7.994439673213343</v>
+      </c>
+      <c r="D89">
+        <v>26.69279032678667</v>
+      </c>
+      <c r="E89">
+        <v>62.45823000000001</v>
+      </c>
+      <c r="F89">
+        <v>63.18723000000001</v>
+      </c>
+      <c r="G89">
+        <v>28.5</v>
+      </c>
+      <c r="H89">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>3.71</v>
+      </c>
+      <c r="K89">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L89">
+        <v>2.93</v>
+      </c>
+      <c r="M89">
+        <v>15.089110524</v>
+      </c>
+      <c r="N89">
+        <v>-12.159110524</v>
+      </c>
+      <c r="O89">
+        <v>-3.647733157200001</v>
+      </c>
+      <c r="P89">
+        <v>-8.511377366800001</v>
+      </c>
+      <c r="Q89">
+        <v>-7.731377366800002</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>1.720273703619714</v>
+      </c>
+      <c r="T89">
+        <v>9.814642423793449</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.05825393078020773</v>
+      </c>
+      <c r="W89">
+        <v>0.2248889613296864</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.194179769267359</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.4212889778273901</v>
+      </c>
+      <c r="C90">
+        <v>-8.860303840701278</v>
+      </c>
+      <c r="D90">
+        <v>26.55321615929873</v>
+      </c>
+      <c r="E90">
+        <v>63.18452000000001</v>
+      </c>
+      <c r="F90">
+        <v>63.91352000000001</v>
+      </c>
+      <c r="G90">
+        <v>28.5</v>
+      </c>
+      <c r="H90">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>3.71</v>
+      </c>
+      <c r="K90">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L90">
+        <v>2.93</v>
+      </c>
+      <c r="M90">
+        <v>15.262548576</v>
+      </c>
+      <c r="N90">
+        <v>-12.332548576</v>
+      </c>
+      <c r="O90">
+        <v>-3.699764572800001</v>
+      </c>
+      <c r="P90">
+        <v>-8.632784003200001</v>
+      </c>
+      <c r="Q90">
+        <v>-7.852784003200002</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>1.860396512254691</v>
+      </c>
+      <c r="T90">
+        <v>10.63252929244291</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.05759195429406901</v>
+      </c>
+      <c r="W90">
+        <v>0.2250470413145763</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.19197318098023</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.4232889778273901</v>
+      </c>
+      <c r="C91">
+        <v>-9.72471595962049</v>
+      </c>
+      <c r="D91">
+        <v>26.41509404037952</v>
+      </c>
+      <c r="E91">
+        <v>63.91081000000001</v>
+      </c>
+      <c r="F91">
+        <v>64.63981000000001</v>
+      </c>
+      <c r="G91">
+        <v>28.5</v>
+      </c>
+      <c r="H91">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>3.71</v>
+      </c>
+      <c r="K91">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L91">
+        <v>2.93</v>
+      </c>
+      <c r="M91">
+        <v>15.435986628</v>
+      </c>
+      <c r="N91">
+        <v>-12.505986628</v>
+      </c>
+      <c r="O91">
+        <v>-3.751795988400002</v>
+      </c>
+      <c r="P91">
+        <v>-8.754190639600003</v>
+      </c>
+      <c r="Q91">
+        <v>-7.974190639600003</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>2.025996195186936</v>
+      </c>
+      <c r="T91">
+        <v>11.59912286448317</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.05694485368402329</v>
+      </c>
+      <c r="W91">
+        <v>0.2252015689402553</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.1898161789467442</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.4252889778273901</v>
+      </c>
+      <c r="C92">
+        <v>-10.5876985721181</v>
+      </c>
+      <c r="D92">
+        <v>26.2784014278819</v>
+      </c>
+      <c r="E92">
+        <v>64.6371</v>
+      </c>
+      <c r="F92">
+        <v>65.3661</v>
+      </c>
+      <c r="G92">
+        <v>28.5</v>
+      </c>
+      <c r="H92">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>3.71</v>
+      </c>
+      <c r="K92">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L92">
+        <v>2.93</v>
+      </c>
+      <c r="M92">
+        <v>15.60942468</v>
+      </c>
+      <c r="N92">
+        <v>-12.67942468</v>
+      </c>
+      <c r="O92">
+        <v>-3.803827404000001</v>
+      </c>
+      <c r="P92">
+        <v>-8.875597276000001</v>
+      </c>
+      <c r="Q92">
+        <v>-8.095597276000001</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>2.224715814705629</v>
+      </c>
+      <c r="T92">
+        <v>12.75903515093149</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.05631213308753414</v>
+      </c>
+      <c r="W92">
+        <v>0.2253526626186969</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.1877071102917804</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.4272889778273901</v>
+      </c>
+      <c r="C93">
+        <v>-11.44927375613976</v>
+      </c>
+      <c r="D93">
+        <v>26.14311624386024</v>
+      </c>
+      <c r="E93">
+        <v>65.36339000000001</v>
+      </c>
+      <c r="F93">
+        <v>66.09239000000001</v>
+      </c>
+      <c r="G93">
+        <v>28.5</v>
+      </c>
+      <c r="H93">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>3.71</v>
+      </c>
+      <c r="K93">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L93">
+        <v>2.93</v>
+      </c>
+      <c r="M93">
+        <v>15.782862732</v>
+      </c>
+      <c r="N93">
+        <v>-12.852862732</v>
+      </c>
+      <c r="O93">
+        <v>-3.855858819600002</v>
+      </c>
+      <c r="P93">
+        <v>-8.997003912400002</v>
+      </c>
+      <c r="Q93">
+        <v>-8.217003912400003</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>2.467595349672921</v>
+      </c>
+      <c r="T93">
+        <v>14.17670572325721</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.05569331843822058</v>
+      </c>
+      <c r="W93">
+        <v>0.225500435556953</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.1856443947940686</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.4292889778273901</v>
+      </c>
+      <c r="C94">
+        <v>-12.30946313731725</v>
+      </c>
+      <c r="D94">
+        <v>26.00921686268275</v>
+      </c>
+      <c r="E94">
+        <v>66.08968</v>
+      </c>
+      <c r="F94">
+        <v>66.81868</v>
+      </c>
+      <c r="G94">
+        <v>28.5</v>
+      </c>
+      <c r="H94">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>3.71</v>
+      </c>
+      <c r="K94">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L94">
+        <v>2.93</v>
+      </c>
+      <c r="M94">
+        <v>15.956300784</v>
+      </c>
+      <c r="N94">
+        <v>-13.026300784</v>
+      </c>
+      <c r="O94">
+        <v>-3.907890235200001</v>
+      </c>
+      <c r="P94">
+        <v>-9.1184105488</v>
+      </c>
+      <c r="Q94">
+        <v>-8.338410548800001</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>2.771194768382038</v>
+      </c>
+      <c r="T94">
+        <v>15.94879393866437</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.0550879562812834</v>
+      </c>
+      <c r="W94">
+        <v>0.2256449960400295</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.1836265209376113</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.4312889778273901</v>
+      </c>
+      <c r="C95">
+        <v>-13.1682879004928</v>
+      </c>
+      <c r="D95">
+        <v>25.87668209950721</v>
+      </c>
+      <c r="E95">
+        <v>66.81597000000001</v>
+      </c>
+      <c r="F95">
+        <v>67.54497000000001</v>
+      </c>
+      <c r="G95">
+        <v>28.5</v>
+      </c>
+      <c r="H95">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>3.71</v>
+      </c>
+      <c r="K95">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L95">
+        <v>2.93</v>
+      </c>
+      <c r="M95">
+        <v>16.129738836</v>
+      </c>
+      <c r="N95">
+        <v>-13.199738836</v>
+      </c>
+      <c r="O95">
+        <v>-3.959921650800001</v>
+      </c>
+      <c r="P95">
+        <v>-9.2398171852</v>
+      </c>
+      <c r="Q95">
+        <v>-8.4598171852</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>3.161536878150901</v>
+      </c>
+      <c r="T95">
+        <v>18.22719307275928</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.05449561266535562</v>
+      </c>
+      <c r="W95">
+        <v>0.2257864476955131</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.181652042217852</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.4332889778273901</v>
+      </c>
+      <c r="C96">
+        <v>-14.02576880089272</v>
+      </c>
+      <c r="D96">
+        <v>25.7454911991073</v>
+      </c>
+      <c r="E96">
+        <v>67.54226000000001</v>
+      </c>
+      <c r="F96">
+        <v>68.27126000000001</v>
+      </c>
+      <c r="G96">
+        <v>28.5</v>
+      </c>
+      <c r="H96">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>3.71</v>
+      </c>
+      <c r="K96">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L96">
+        <v>2.93</v>
+      </c>
+      <c r="M96">
+        <v>16.303176888</v>
+      </c>
+      <c r="N96">
+        <v>-13.373176888</v>
+      </c>
+      <c r="O96">
+        <v>-4.011953066400001</v>
+      </c>
+      <c r="P96">
+        <v>-9.361223821600003</v>
+      </c>
+      <c r="Q96">
+        <v>-8.581223821600004</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>3.681993024509385</v>
+      </c>
+      <c r="T96">
+        <v>21.26505858488583</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.05391587210508588</v>
+      </c>
+      <c r="W96">
+        <v>0.2259248897413055</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.1797195736836196</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.4352889778273901</v>
+      </c>
+      <c r="C97">
+        <v>-14.88192617496289</v>
+      </c>
+      <c r="D97">
+        <v>25.61562382503711</v>
+      </c>
+      <c r="E97">
+        <v>68.26855</v>
+      </c>
+      <c r="F97">
+        <v>68.99755</v>
+      </c>
+      <c r="G97">
+        <v>28.5</v>
+      </c>
+      <c r="H97">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>3.71</v>
+      </c>
+      <c r="K97">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L97">
+        <v>2.93</v>
+      </c>
+      <c r="M97">
+        <v>16.47661494</v>
+      </c>
+      <c r="N97">
+        <v>-13.54661494</v>
+      </c>
+      <c r="O97">
+        <v>-4.063984482000001</v>
+      </c>
+      <c r="P97">
+        <v>-9.482630457999999</v>
+      </c>
+      <c r="Q97">
+        <v>-8.702630458</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>4.410631629411264</v>
+      </c>
+      <c r="T97">
+        <v>25.51807030186301</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.05334833660924287</v>
+      </c>
+      <c r="W97">
+        <v>0.2260604172177128</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.1778277886974762</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.4372889778273901</v>
+      </c>
+      <c r="C98">
+        <v>-15.73677995087807</v>
+      </c>
+      <c r="D98">
+        <v>25.48706004912192</v>
+      </c>
+      <c r="E98">
+        <v>68.99484</v>
+      </c>
+      <c r="F98">
+        <v>69.72384</v>
+      </c>
+      <c r="G98">
+        <v>28.5</v>
+      </c>
+      <c r="H98">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>3.71</v>
+      </c>
+      <c r="K98">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L98">
+        <v>2.93</v>
+      </c>
+      <c r="M98">
+        <v>16.650052992</v>
+      </c>
+      <c r="N98">
+        <v>-13.720052992</v>
+      </c>
+      <c r="O98">
+        <v>-4.116015897600001</v>
+      </c>
+      <c r="P98">
+        <v>-9.604037094399999</v>
+      </c>
+      <c r="Q98">
+        <v>-8.8240370944</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>5.503589536764068</v>
+      </c>
+      <c r="T98">
+        <v>31.89758787732869</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.05279262476956327</v>
+      </c>
+      <c r="W98">
+        <v>0.2261931212050283</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.1759754158985442</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.4392889778273901</v>
+      </c>
+      <c r="C99">
+        <v>-16.59034965873614</v>
+      </c>
+      <c r="D99">
+        <v>25.35978034126386</v>
+      </c>
+      <c r="E99">
+        <v>69.72113</v>
+      </c>
+      <c r="F99">
+        <v>70.45013</v>
+      </c>
+      <c r="G99">
+        <v>28.5</v>
+      </c>
+      <c r="H99">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>3.71</v>
+      </c>
+      <c r="K99">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L99">
+        <v>2.93</v>
+      </c>
+      <c r="M99">
+        <v>16.823491044</v>
+      </c>
+      <c r="N99">
+        <v>-13.893491044</v>
+      </c>
+      <c r="O99">
+        <v>-4.168047313200001</v>
+      </c>
+      <c r="P99">
+        <v>-9.7254437308</v>
+      </c>
+      <c r="Q99">
+        <v>-8.945443730800001</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>7.325186049018757</v>
+      </c>
+      <c r="T99">
+        <v>42.53011716977158</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.05224837090595952</v>
+      </c>
+      <c r="W99">
+        <v>0.2263230890276569</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.1741612363531984</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.4412889778273901</v>
+      </c>
+      <c r="C100">
+        <v>-17.44265444044845</v>
+      </c>
+      <c r="D100">
+        <v>25.23376555955155</v>
+      </c>
+      <c r="E100">
+        <v>70.44742000000001</v>
+      </c>
+      <c r="F100">
+        <v>71.17642000000001</v>
+      </c>
+      <c r="G100">
+        <v>28.5</v>
+      </c>
+      <c r="H100">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>3.71</v>
+      </c>
+      <c r="K100">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L100">
+        <v>2.93</v>
+      </c>
+      <c r="M100">
+        <v>16.996929096</v>
+      </c>
+      <c r="N100">
+        <v>-14.066929096</v>
+      </c>
+      <c r="O100">
+        <v>-4.220078728800002</v>
+      </c>
+      <c r="P100">
+        <v>-9.846850367200002</v>
+      </c>
+      <c r="Q100">
+        <v>-9.066850367200002</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>10.96837907352814</v>
+      </c>
+      <c r="T100">
+        <v>63.79517575465737</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.05171522426406197</v>
+      </c>
+      <c r="W100">
+        <v>0.226450404445742</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.1723840808802065</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.4432889778273901</v>
+      </c>
+      <c r="C101">
+        <v>-18.29371305933684</v>
+      </c>
+      <c r="D101">
+        <v>25.10899694066316</v>
+      </c>
+      <c r="E101">
+        <v>71.17371</v>
+      </c>
+      <c r="F101">
+        <v>71.90271</v>
+      </c>
+      <c r="G101">
+        <v>28.5</v>
+      </c>
+      <c r="H101">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>3.71</v>
+      </c>
+      <c r="K101">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="L101">
+        <v>2.93</v>
+      </c>
+      <c r="M101">
+        <v>17.170367148</v>
+      </c>
+      <c r="N101">
+        <v>-14.240367148</v>
+      </c>
+      <c r="O101">
+        <v>-4.272110144400001</v>
+      </c>
+      <c r="P101">
+        <v>-9.9682570036</v>
+      </c>
+      <c r="Q101">
+        <v>-9.1882570036</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>21.89795814705627</v>
+      </c>
+      <c r="T101">
+        <v>127.5903515093147</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.05119284826139468</v>
+      </c>
+      <c r="W101">
+        <v>0.226575147835179</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.1706428275379822</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
